--- a/2.DIAGRAMAS/PPP.xlsx
+++ b/2.DIAGRAMAS/PPP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aprendiz\Documents\ADSO, 2006\PROYECTO_ADSO_KJGA\2.DIAGRAMAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FD9CC25-4A05-4439-A40C-F08C45919A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C1A8F4-D7C3-499C-BBE0-5F74F4993DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26640" windowHeight="13170" activeTab="1" xr2:uid="{D1012828-DDFC-47C0-86DB-3A2BD43233B1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D1012828-DDFC-47C0-86DB-3A2BD43233B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Normal" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="338">
   <si>
     <t>Fundación</t>
   </si>
@@ -313,12 +313,6 @@
     <t>Marcela</t>
   </si>
   <si>
-    <t>tipo_User</t>
-  </si>
-  <si>
-    <t>tipo_Doc</t>
-  </si>
-  <si>
     <t>num_Doc</t>
   </si>
   <si>
@@ -976,39 +970,6 @@
     <t>foto20.jpg</t>
   </si>
   <si>
-    <t>foto21.jpg</t>
-  </si>
-  <si>
-    <t>foto22.jpg</t>
-  </si>
-  <si>
-    <t>foto23.jpg</t>
-  </si>
-  <si>
-    <t>foto24.jpg</t>
-  </si>
-  <si>
-    <t>foto25.jpg</t>
-  </si>
-  <si>
-    <t>foto26.jpg</t>
-  </si>
-  <si>
-    <t>foto27.jpg</t>
-  </si>
-  <si>
-    <t>foto28.jpg</t>
-  </si>
-  <si>
-    <t>foto29.jpg</t>
-  </si>
-  <si>
-    <t>foto30.jpg</t>
-  </si>
-  <si>
-    <t>tipo_Public</t>
-  </si>
-  <si>
     <t>especie</t>
   </si>
   <si>
@@ -1070,13 +1031,37 @@
   </si>
   <si>
     <t>Daisy</t>
+  </si>
+  <si>
+    <t>Kira</t>
+  </si>
+  <si>
+    <t>Canela</t>
+  </si>
+  <si>
+    <t>mascota nombre</t>
+  </si>
+  <si>
+    <t>tip_Doc</t>
+  </si>
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>apellido</t>
+  </si>
+  <si>
+    <t>tip_User</t>
+  </si>
+  <si>
+    <t>tip_Public</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1167,35 +1152,22 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <color theme="0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="9"/>
-      <color theme="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <u/>
-      <sz val="9"/>
+      <sz val="10"/>
       <color theme="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -1346,7 +1318,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1376,12 +1348,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1394,31 +1360,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1427,7 +1372,6 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="9" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1446,34 +1390,31 @@
     <xf numFmtId="0" fontId="12" fillId="8" borderId="5" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1482,7 +1423,30 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="20% - Énfasis1" xfId="2" builtinId="30"/>
@@ -1826,328 +1790,347 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53CAFCBD-51ED-4D7F-B584-3F5A2EED76BE}">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
     <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+    </row>
+    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="H2" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="B2" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="D2" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="E2" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="27" t="s">
+      <c r="I2" s="43" t="s">
+        <v>332</v>
+      </c>
+      <c r="J2" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="K2" s="18" t="s">
         <v>259</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="L2" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="M2" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="N2" s="18" t="s">
         <v>262</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="O2" s="22" t="s">
         <v>263</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="P2" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="N2" s="32" t="s">
-        <v>265</v>
-      </c>
-      <c r="O2" s="32" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>191</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>193</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="K3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="L3" s="1" t="s">
+      <c r="N3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H4" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>197</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>199</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>278</v>
+        <v>266</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>319</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="L5" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>200</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>202</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>280</v>
+        <v>272</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>320</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="L6" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>203</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>205</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>282</v>
+        <v>266</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>321</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>139</v>
+        <v>280</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>283</v>
+        <v>137</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>3</v>
       </c>
@@ -2155,93 +2138,99 @@
         <v>11</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>284</v>
+        <v>272</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>322</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="L8" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P8" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>208</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>210</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>286</v>
+        <v>266</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>323</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="L9" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>3</v>
       </c>
@@ -2249,46 +2238,49 @@
         <v>14</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>288</v>
+        <v>272</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>324</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="L10" s="1" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>3</v>
       </c>
@@ -2296,46 +2288,49 @@
         <v>16</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>290</v>
+        <v>266</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J11" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="L11" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P11" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>3</v>
       </c>
@@ -2343,140 +2338,149 @@
         <v>18</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>292</v>
+        <v>272</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>326</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>139</v>
+        <v>290</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>293</v>
+        <v>137</v>
       </c>
       <c r="L12" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P12" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="M12" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>217</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>219</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N13" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C14" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>218</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>220</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="M14" s="30">
+      <c r="N14" s="20">
         <v>46280.375</v>
       </c>
-      <c r="N14" s="31">
+      <c r="O14" s="21">
         <v>46280.541666666664</v>
       </c>
-      <c r="O14" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P14" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>20</v>
       </c>
@@ -2484,46 +2488,49 @@
         <v>26</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>28</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>328</v>
       </c>
       <c r="J15" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="L15" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>272</v>
+        <v>299</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>20</v>
       </c>
@@ -2531,140 +2538,149 @@
         <v>26</v>
       </c>
       <c r="C16" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>221</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>223</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>28</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>270</v>
       </c>
       <c r="J16" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="L16" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="M16" s="30">
+        <v>300</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="N16" s="20">
         <v>46254.416666666664</v>
       </c>
-      <c r="N16" s="31">
+      <c r="O16" s="21">
         <v>46254.583333333336</v>
       </c>
-      <c r="O16" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P16" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>224</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>226</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="M17" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>272</v>
+      <c r="N17" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C18" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>225</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>227</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>270</v>
       </c>
       <c r="J18" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="L18" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="M18" s="30">
+        <v>303</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="N18" s="20">
         <v>46275.333333333336</v>
       </c>
-      <c r="N18" s="31">
+      <c r="O18" s="21">
         <v>46275.5</v>
       </c>
-      <c r="O18" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>20</v>
       </c>
@@ -2672,46 +2688,49 @@
         <v>37</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="M19" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>272</v>
+      <c r="N19" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>20</v>
       </c>
@@ -2719,46 +2738,49 @@
         <v>37</v>
       </c>
       <c r="C20" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>228</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>230</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="M20" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="M20" s="30">
+      <c r="N20" s="20">
         <v>46283.458333333336</v>
       </c>
-      <c r="N20" s="31">
+      <c r="O20" s="21">
         <v>46283.625</v>
       </c>
-      <c r="O20" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P20" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>20</v>
       </c>
@@ -2766,46 +2788,49 @@
         <v>40</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>42</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>282</v>
+        <v>266</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>331</v>
       </c>
       <c r="J21" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="L21" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>272</v>
+        <v>299</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>20</v>
       </c>
@@ -2813,93 +2838,99 @@
         <v>40</v>
       </c>
       <c r="C22" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>231</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>233</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>42</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>270</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>139</v>
+        <v>270</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>310</v>
+        <v>137</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="M22" s="31">
+        <v>308</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="N22" s="21">
         <v>46259.375</v>
       </c>
-      <c r="N22" s="31">
+      <c r="O22" s="21">
         <v>46259.541666666664</v>
       </c>
-      <c r="O22" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B23" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G23" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="M23" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>272</v>
+      <c r="N23" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>2</v>
       </c>
@@ -2907,46 +2938,49 @@
         <v>25</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G24" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="M24" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="H24" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="M24" s="31">
-        <v>46287.375</v>
-      </c>
-      <c r="N24" s="31">
-        <v>46287.5</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N24" s="20">
+        <v>46280.375</v>
+      </c>
+      <c r="O24" s="21">
+        <v>46280.541666666664</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>2</v>
       </c>
@@ -2954,46 +2988,49 @@
         <v>30</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>28</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="J25" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="K25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K25" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>272</v>
+      <c r="L25" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>2</v>
       </c>
@@ -3001,46 +3038,49 @@
         <v>32</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>28</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="J26" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K26" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="M26" s="31">
-        <v>46277.416666666664</v>
-      </c>
-      <c r="N26" s="31">
-        <v>46277.583333333336</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L26" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="N26" s="20">
+        <v>46254.416666666664</v>
+      </c>
+      <c r="O26" s="21">
+        <v>46254.583333333336</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>2</v>
       </c>
@@ -3048,93 +3088,99 @@
         <v>34</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G27" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="M27" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>272</v>
+      <c r="N27" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B28" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>245</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>247</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="J28" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="L28" s="2" t="s">
+      <c r="L28" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="M28" s="31">
-        <v>46262.375</v>
-      </c>
-      <c r="N28" s="31">
-        <v>46262.541666666664</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M28" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="N28" s="20">
+        <v>46275.333333333336</v>
+      </c>
+      <c r="O28" s="21">
+        <v>46275.5</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>2</v>
       </c>
@@ -3142,46 +3188,49 @@
         <v>36</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>35</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G29" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="M29" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>272</v>
+      <c r="N29" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>2</v>
       </c>
@@ -3189,93 +3238,99 @@
         <v>39</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>35</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G30" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="M30" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="M30" s="31">
-        <v>46290.333333333336</v>
-      </c>
-      <c r="N30" s="31">
-        <v>46290.5</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N30" s="20">
+        <v>46283.458333333336</v>
+      </c>
+      <c r="O30" s="21">
+        <v>46283.625</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B31" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>252</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>254</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>42</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="J31" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="K31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K31" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>272</v>
+      <c r="L31" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>2</v>
       </c>
@@ -3283,48 +3338,51 @@
         <v>44</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>42</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>270</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>139</v>
+        <v>270</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>320</v>
+        <v>137</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="M32" s="31">
-        <v>46264.416666666664</v>
-      </c>
-      <c r="N32" s="31">
-        <v>46264.583333333336</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>273</v>
+        <v>308</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="N32" s="21">
+        <v>46259.375</v>
+      </c>
+      <c r="O32" s="21">
+        <v>46259.541666666664</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3335,1841 +3393,1876 @@
   <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="8.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="20" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A1" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+    </row>
+    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>333</v>
+      </c>
+      <c r="E2" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="35" t="s">
+      <c r="F2" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="G2" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="H2" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="I2" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="H2" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="I2" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="J2" s="43" t="s">
+      <c r="J2" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="K2" s="39" t="s">
+        <v>317</v>
+      </c>
+      <c r="L2" s="38" t="s">
+        <v>309</v>
+      </c>
+      <c r="M2" s="38" t="s">
+        <v>310</v>
+      </c>
+      <c r="N2" s="38" t="s">
+        <v>311</v>
+      </c>
+      <c r="O2" s="39" t="s">
+        <v>312</v>
+      </c>
+      <c r="P2" s="39" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q2" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="R2" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="S2" s="39" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="8">
+        <v>1001001001</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="8">
+        <v>3001001001</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1001001002</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="8">
+        <v>3001001002</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1001001003</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="8">
+        <v>3001001003</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="8">
+        <v>1001001004</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="8">
+        <v>3001001004</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q6" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R6" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1001001005</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="8">
+        <v>3001001005</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="K7" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="K2" s="47" t="s">
-        <v>330</v>
-      </c>
-      <c r="L2" s="43" t="s">
+      <c r="L7" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1001001006</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="8">
+        <v>3001001006</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="K8" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="M2" s="43" t="s">
+      <c r="L8" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R8" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1001001007</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="8">
+        <v>3001001007</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="K9" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="N2" s="43" t="s">
+      <c r="L9" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1001001008</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="8">
+        <v>3001001008</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="K10" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="O2" s="44" t="s">
+      <c r="L10" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R10" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1001001009</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="8">
+        <v>3001001009</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="K11" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="P2" s="44" t="s">
+      <c r="L11" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q11" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R11" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1001001010</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="8">
+        <v>3001001010</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="K12" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="Q2" s="44" t="s">
-        <v>327</v>
-      </c>
-      <c r="R2" s="44" t="s">
-        <v>328</v>
-      </c>
-      <c r="S2" s="44" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="37" t="s">
+      <c r="L12" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R12" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="37">
-        <v>1001001001</v>
-      </c>
-      <c r="F3" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="37">
-        <v>3001001001</v>
-      </c>
-      <c r="H3" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="K3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="M3" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="N3" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="O3" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="P3" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q3" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R3" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S3" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="37">
-        <v>1001001002</v>
-      </c>
-      <c r="F4" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="37">
-        <v>3001001002</v>
-      </c>
-      <c r="H4" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="K4" t="s">
-        <v>331</v>
-      </c>
-      <c r="L4" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="M4" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="N4" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="O4" s="37" t="s">
-        <v>276</v>
-      </c>
-      <c r="P4" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q4" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R4" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S4" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="37">
-        <v>1001001003</v>
-      </c>
-      <c r="F5" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="37">
-        <v>3001001003</v>
-      </c>
-      <c r="H5" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="K5" t="s">
-        <v>332</v>
-      </c>
-      <c r="L5" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="M5" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="N5" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="P5" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q5" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R5" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S5" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="37">
-        <v>1001001004</v>
-      </c>
-      <c r="F6" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="37">
-        <v>3001001004</v>
-      </c>
-      <c r="H6" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="J6" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="K6" t="s">
-        <v>333</v>
-      </c>
-      <c r="L6" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="M6" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="N6" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="O6" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="P6" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q6" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R6" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S6" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="37">
-        <v>1001001005</v>
-      </c>
-      <c r="F7" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="37">
-        <v>3001001005</v>
-      </c>
-      <c r="H7" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="K7" t="s">
-        <v>334</v>
-      </c>
-      <c r="L7" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="M7" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="N7" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="O7" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="P7" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q7" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R7" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S7" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="37">
-        <v>1001001006</v>
-      </c>
-      <c r="F8" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="37">
-        <v>3001001006</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="I8" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="J8" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="K8" t="s">
-        <v>335</v>
-      </c>
-      <c r="L8" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="M8" s="37" t="s">
-        <v>284</v>
-      </c>
-      <c r="N8" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="O8" s="37" t="s">
-        <v>285</v>
-      </c>
-      <c r="P8" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q8" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R8" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S8" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="37">
-        <v>1001001007</v>
-      </c>
-      <c r="F9" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="37">
-        <v>3001001007</v>
-      </c>
-      <c r="H9" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="K9" t="s">
-        <v>336</v>
-      </c>
-      <c r="L9" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="M9" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="N9" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="O9" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="P9" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q9" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R9" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S9" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="37">
-        <v>1001001008</v>
-      </c>
-      <c r="F10" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="37">
-        <v>3001001008</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="I10" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="J10" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="K10" t="s">
-        <v>337</v>
-      </c>
-      <c r="L10" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="M10" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="N10" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="O10" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="P10" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q10" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R10" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S10" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="37">
-        <v>1001001009</v>
-      </c>
-      <c r="F11" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="37">
-        <v>3001001009</v>
-      </c>
-      <c r="H11" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="I11" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="J11" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="K11" t="s">
-        <v>338</v>
-      </c>
-      <c r="L11" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="M11" s="37" t="s">
-        <v>290</v>
-      </c>
-      <c r="N11" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="O11" s="37" t="s">
-        <v>291</v>
-      </c>
-      <c r="P11" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q11" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R11" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S11" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A12" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="37">
-        <v>1001001010</v>
-      </c>
-      <c r="F12" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="37">
-        <v>3001001010</v>
-      </c>
-      <c r="H12" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="I12" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="J12" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="K12" t="s">
-        <v>339</v>
-      </c>
-      <c r="L12" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="M12" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="N12" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="O12" s="37" t="s">
-        <v>293</v>
-      </c>
-      <c r="P12" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q12" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R12" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S12" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="37">
+      <c r="E13" s="8">
         <v>1002001001</v>
       </c>
       <c r="F13" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="8">
         <v>3102001001</v>
       </c>
-      <c r="H13" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="I13" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="J13" s="37" t="s">
+      <c r="H13" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O13" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="P13" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="K13" t="s">
-        <v>340</v>
-      </c>
-      <c r="L13" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="M13" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="N13" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="O13" s="40" t="s">
-        <v>295</v>
-      </c>
-      <c r="P13" s="38" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q13" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R13" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S13" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+      <c r="Q13" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S13" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="37">
+      <c r="E14" s="8">
         <v>1002001001</v>
       </c>
       <c r="F14" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="8">
         <v>3102001001</v>
       </c>
-      <c r="H14" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="I14" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="J14" s="37" t="s">
+      <c r="H14" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" s="40" t="s">
+        <v>296</v>
+      </c>
+      <c r="P14" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="K14" s="28"/>
-      <c r="L14" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="M14" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="N14" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="O14" s="40" t="s">
-        <v>298</v>
-      </c>
-      <c r="P14" s="38" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q14" s="42">
+      <c r="Q14" s="41">
         <v>46280.375</v>
       </c>
-      <c r="R14" s="42">
+      <c r="R14" s="41">
         <v>46280.541666666664</v>
       </c>
-      <c r="S14" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="37" t="s">
+      <c r="S14" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="8">
         <v>1002001003</v>
       </c>
       <c r="F15" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="8">
         <v>3102001003</v>
       </c>
-      <c r="H15" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="I15" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="J15" s="37" t="s">
-        <v>294</v>
-      </c>
-      <c r="K15" t="s">
-        <v>341</v>
-      </c>
-      <c r="L15" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="M15" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="N15" s="37" t="s">
+      <c r="H15" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="N15" s="8" t="s">
         <v>29</v>
       </c>
       <c r="O15" s="40" t="s">
-        <v>300</v>
-      </c>
-      <c r="P15" s="38" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q15" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R15" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S15" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
+        <v>298</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q15" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R15" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="D16" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="37">
+      <c r="E16" s="8">
         <v>1002001003</v>
       </c>
       <c r="F16" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="37">
+      <c r="G16" s="8">
         <v>3102001003</v>
       </c>
-      <c r="H16" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="I16" s="38" t="s">
+      <c r="H16" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O16" s="40" t="s">
+        <v>300</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q16" s="41">
+        <v>46254.416666666664</v>
+      </c>
+      <c r="R16" s="41">
+        <v>46254.583333333336</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1002001005</v>
+      </c>
+      <c r="F17" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="G17" s="8">
+        <v>3102001005</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="O17" s="40" t="s">
+        <v>302</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q17" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R17" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S17" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1002001005</v>
+      </c>
+      <c r="F18" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="G18" s="8">
+        <v>3102001005</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="I18" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="J16" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="K16" s="28"/>
-      <c r="L16" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="M16" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="N16" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="O16" s="40" t="s">
-        <v>302</v>
-      </c>
-      <c r="P16" s="38" t="s">
+      <c r="J18" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O18" s="40" t="s">
         <v>303</v>
       </c>
-      <c r="Q16" s="42">
-        <v>46254.416666666664</v>
-      </c>
-      <c r="R16" s="42">
-        <v>46254.583333333336</v>
-      </c>
-      <c r="S16" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
+      <c r="P18" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q18" s="41">
+        <v>46275.333333333336</v>
+      </c>
+      <c r="R18" s="41">
+        <v>46275.5</v>
+      </c>
+      <c r="S18" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="37" t="s">
+      <c r="B19" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="37">
-        <v>1002001005</v>
-      </c>
-      <c r="F17" s="40" t="s">
-        <v>186</v>
-      </c>
-      <c r="G17" s="37">
-        <v>3102001005</v>
-      </c>
-      <c r="H17" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="I17" s="38" t="s">
-        <v>150</v>
-      </c>
-      <c r="J17" s="37" t="s">
-        <v>294</v>
-      </c>
-      <c r="K17" t="s">
-        <v>342</v>
-      </c>
-      <c r="L17" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="M17" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="N17" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="O17" s="40" t="s">
-        <v>304</v>
-      </c>
-      <c r="P17" s="38" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q17" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R17" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S17" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="37">
-        <v>1002001005</v>
-      </c>
-      <c r="F18" s="40" t="s">
-        <v>186</v>
-      </c>
-      <c r="G18" s="37">
-        <v>3102001005</v>
-      </c>
-      <c r="H18" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="I18" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="J18" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="K18" s="28"/>
-      <c r="L18" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="M18" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="N18" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="O18" s="40" t="s">
-        <v>305</v>
-      </c>
-      <c r="P18" s="38" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q18" s="42">
-        <v>46275.333333333336</v>
-      </c>
-      <c r="R18" s="42">
-        <v>46275.5</v>
-      </c>
-      <c r="S18" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" s="37">
+      <c r="E19" s="8">
         <v>1002001007</v>
       </c>
       <c r="F19" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="G19" s="37">
+      <c r="G19" s="8">
         <v>3102001007</v>
       </c>
-      <c r="H19" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="I19" s="38" t="s">
-        <v>152</v>
-      </c>
-      <c r="J19" s="37" t="s">
+      <c r="H19" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O19" s="40" t="s">
+        <v>305</v>
+      </c>
+      <c r="P19" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="K19" s="28"/>
-      <c r="L19" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="N19" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="O19" s="40" t="s">
-        <v>307</v>
-      </c>
-      <c r="P19" s="38" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q19" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R19" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S19" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="37" t="s">
+      <c r="Q19" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R19" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S19" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="D20" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="37">
+      <c r="E20" s="8">
         <v>1002001007</v>
       </c>
       <c r="F20" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="G20" s="37">
+      <c r="G20" s="8">
         <v>3102001007</v>
       </c>
-      <c r="H20" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="I20" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="J20" s="37" t="s">
+      <c r="H20" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O20" s="40" t="s">
+        <v>306</v>
+      </c>
+      <c r="P20" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="K20" s="28"/>
-      <c r="L20" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="M20" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="N20" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="O20" s="40" t="s">
-        <v>308</v>
-      </c>
-      <c r="P20" s="38" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q20" s="42">
+      <c r="Q20" s="41">
         <v>46283.458333333336</v>
       </c>
-      <c r="R20" s="42">
+      <c r="R20" s="41">
         <v>46283.625</v>
       </c>
-      <c r="S20" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="37" t="s">
+      <c r="S20" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="37" t="s">
+      <c r="D21" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="37">
+      <c r="E21" s="8">
         <v>1002001009</v>
       </c>
       <c r="F21" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="G21" s="37">
+      <c r="G21" s="8">
         <v>3102001009</v>
       </c>
-      <c r="H21" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="I21" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="J21" s="37" t="s">
-        <v>294</v>
-      </c>
-      <c r="K21" s="28"/>
-      <c r="L21" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="M21" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="N21" s="37" t="s">
+      <c r="H21" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="N21" s="8" t="s">
         <v>31</v>
       </c>
       <c r="O21" s="40" t="s">
-        <v>309</v>
-      </c>
-      <c r="P21" s="38" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q21" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R21" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S21" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="P21" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q21" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R21" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S21" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="37" t="s">
+      <c r="D22" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="37">
+      <c r="E22" s="8">
         <v>1002001009</v>
       </c>
       <c r="F22" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="G22" s="37">
+      <c r="G22" s="8">
         <v>3102001009</v>
       </c>
-      <c r="H22" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="I22" s="38" t="s">
-        <v>155</v>
-      </c>
-      <c r="J22" s="37" t="s">
+      <c r="H22" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="O22" s="40" t="s">
+        <v>308</v>
+      </c>
+      <c r="P22" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q22" s="41">
+        <v>46259.375</v>
+      </c>
+      <c r="R22" s="41">
+        <v>46259.541666666664</v>
+      </c>
+      <c r="S22" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1003001001</v>
+      </c>
+      <c r="F23" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="G23" s="8">
+        <v>3203001001</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O23" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="P23" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q23" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R23" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S23" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1003001002</v>
+      </c>
+      <c r="F24" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="G24" s="8">
+        <v>3203001002</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O24" s="40" t="s">
+        <v>296</v>
+      </c>
+      <c r="P24" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="K22" s="28"/>
-      <c r="L22" s="37" t="s">
+      <c r="Q24" s="41">
+        <v>46280.375</v>
+      </c>
+      <c r="R24" s="41">
+        <v>46280.541666666664</v>
+      </c>
+      <c r="S24" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1003001003</v>
+      </c>
+      <c r="F25" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="G25" s="8">
+        <v>3203001003</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="L25" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="M22" s="37" t="s">
+      <c r="M25" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O25" s="40" t="s">
+        <v>298</v>
+      </c>
+      <c r="P25" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q25" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R25" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S25" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1003001004</v>
+      </c>
+      <c r="F26" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="G26" s="8">
+        <v>3203001004</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O26" s="40" t="s">
+        <v>300</v>
+      </c>
+      <c r="P26" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q26" s="41">
+        <v>46254.416666666664</v>
+      </c>
+      <c r="R26" s="41">
+        <v>46254.583333333336</v>
+      </c>
+      <c r="S26" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1003001005</v>
+      </c>
+      <c r="F27" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="G27" s="8">
+        <v>3203001005</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="O27" s="40" t="s">
+        <v>302</v>
+      </c>
+      <c r="P27" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q27" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R27" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S27" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E28" s="8">
+        <v>1003001006</v>
+      </c>
+      <c r="F28" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="G28" s="8">
+        <v>3203001006</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O28" s="40" t="s">
+        <v>303</v>
+      </c>
+      <c r="P28" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q28" s="41">
+        <v>46275.333333333336</v>
+      </c>
+      <c r="R28" s="41">
+        <v>46275.5</v>
+      </c>
+      <c r="S28" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1003001007</v>
+      </c>
+      <c r="F29" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="G29" s="8">
+        <v>3203001007</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="L29" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="N22" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="O22" s="40" t="s">
-        <v>310</v>
-      </c>
-      <c r="P22" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q22" s="42">
+      <c r="M29" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O29" s="40" t="s">
+        <v>305</v>
+      </c>
+      <c r="P29" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q29" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R29" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S29" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1003001008</v>
+      </c>
+      <c r="F30" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="G30" s="8">
+        <v>3203001008</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="N30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O30" s="40" t="s">
+        <v>306</v>
+      </c>
+      <c r="P30" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q30" s="41">
+        <v>46283.458333333336</v>
+      </c>
+      <c r="R30" s="41">
+        <v>46283.625</v>
+      </c>
+      <c r="S30" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1003001009</v>
+      </c>
+      <c r="F31" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="G31" s="8">
+        <v>3203001009</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="N31" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O31" s="40" t="s">
+        <v>307</v>
+      </c>
+      <c r="P31" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q31" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R31" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S31" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1003001010</v>
+      </c>
+      <c r="F32" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="G32" s="8">
+        <v>3203001010</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="N32" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="O32" s="40" t="s">
+        <v>308</v>
+      </c>
+      <c r="P32" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q32" s="41">
         <v>46259.375</v>
       </c>
-      <c r="R22" s="42">
+      <c r="R32" s="41">
         <v>46259.541666666664</v>
       </c>
-      <c r="S22" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="B23" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="37">
-        <v>1003001001</v>
-      </c>
-      <c r="F23" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="G23" s="37">
-        <v>3203001001</v>
-      </c>
-      <c r="H23" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="I23" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="J23" s="38" t="s">
-        <v>294</v>
-      </c>
-      <c r="K23" s="28"/>
-      <c r="L23" s="38" t="s">
-        <v>274</v>
-      </c>
-      <c r="M23" s="38" t="s">
-        <v>284</v>
-      </c>
-      <c r="N23" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="O23" s="38" t="s">
-        <v>311</v>
-      </c>
-      <c r="P23" s="38" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q23" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R23" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S23" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="B24" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="37">
-        <v>1003001002</v>
-      </c>
-      <c r="F24" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="G24" s="37">
-        <v>3203001002</v>
-      </c>
-      <c r="H24" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="I24" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="J24" s="38" t="s">
-        <v>297</v>
-      </c>
-      <c r="K24" s="28"/>
-      <c r="L24" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="M24" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="N24" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="O24" s="38" t="s">
-        <v>312</v>
-      </c>
-      <c r="P24" s="38" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q24" s="42">
-        <v>46287.375</v>
-      </c>
-      <c r="R24" s="42">
-        <v>46287.5</v>
-      </c>
-      <c r="S24" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="B25" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="37">
-        <v>1003001003</v>
-      </c>
-      <c r="F25" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G25" s="37">
-        <v>3203001003</v>
-      </c>
-      <c r="H25" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="I25" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="J25" s="38" t="s">
-        <v>294</v>
-      </c>
-      <c r="K25" s="28"/>
-      <c r="L25" s="38" t="s">
-        <v>268</v>
-      </c>
-      <c r="M25" s="38" t="s">
-        <v>286</v>
-      </c>
-      <c r="N25" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="O25" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="P25" s="38" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q25" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R25" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S25" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E26" s="37">
-        <v>1003001004</v>
-      </c>
-      <c r="F26" s="40" t="s">
-        <v>164</v>
-      </c>
-      <c r="G26" s="37">
-        <v>3203001004</v>
-      </c>
-      <c r="H26" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="I26" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="J26" s="38" t="s">
-        <v>297</v>
-      </c>
-      <c r="K26" s="28"/>
-      <c r="L26" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="M26" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="N26" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O26" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="P26" s="38" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q26" s="42">
-        <v>46277.416666666664</v>
-      </c>
-      <c r="R26" s="42">
-        <v>46277.583333333336</v>
-      </c>
-      <c r="S26" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27" s="37">
-        <v>1003001005</v>
-      </c>
-      <c r="F27" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="G27" s="37">
-        <v>3203001005</v>
-      </c>
-      <c r="H27" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="I27" s="38" t="s">
-        <v>150</v>
-      </c>
-      <c r="J27" s="38" t="s">
-        <v>294</v>
-      </c>
-      <c r="K27" s="28"/>
-      <c r="L27" s="38" t="s">
-        <v>268</v>
-      </c>
-      <c r="M27" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="N27" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="O27" s="38" t="s">
-        <v>315</v>
-      </c>
-      <c r="P27" s="38" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q27" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R27" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S27" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E28" s="37">
-        <v>1003001006</v>
-      </c>
-      <c r="F28" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="G28" s="37">
-        <v>3203001006</v>
-      </c>
-      <c r="H28" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="I28" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="J28" s="38" t="s">
-        <v>297</v>
-      </c>
-      <c r="K28" s="28"/>
-      <c r="L28" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="M28" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="N28" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="O28" s="38" t="s">
-        <v>316</v>
-      </c>
-      <c r="P28" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q28" s="42">
-        <v>46262.375</v>
-      </c>
-      <c r="R28" s="42">
-        <v>46262.541666666664</v>
-      </c>
-      <c r="S28" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="B29" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="37">
-        <v>1003001007</v>
-      </c>
-      <c r="F29" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="G29" s="37">
-        <v>3203001007</v>
-      </c>
-      <c r="H29" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="I29" s="38" t="s">
-        <v>152</v>
-      </c>
-      <c r="J29" s="38" t="s">
-        <v>294</v>
-      </c>
-      <c r="K29" s="28"/>
-      <c r="L29" s="38" t="s">
-        <v>274</v>
-      </c>
-      <c r="M29" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="N29" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="O29" s="38" t="s">
-        <v>317</v>
-      </c>
-      <c r="P29" s="38" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q29" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R29" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S29" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="B30" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E30" s="37">
-        <v>1003001008</v>
-      </c>
-      <c r="F30" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="G30" s="37">
-        <v>3203001008</v>
-      </c>
-      <c r="H30" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="I30" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="J30" s="38" t="s">
-        <v>297</v>
-      </c>
-      <c r="K30" s="28"/>
-      <c r="L30" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="M30" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="N30" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="O30" s="38" t="s">
-        <v>318</v>
-      </c>
-      <c r="P30" s="38" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q30" s="42">
-        <v>46290.333333333336</v>
-      </c>
-      <c r="R30" s="42">
-        <v>46290.5</v>
-      </c>
-      <c r="S30" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="B31" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" s="37">
-        <v>1003001009</v>
-      </c>
-      <c r="F31" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="G31" s="37">
-        <v>3203001009</v>
-      </c>
-      <c r="H31" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="I31" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="J31" s="38" t="s">
-        <v>294</v>
-      </c>
-      <c r="K31" s="28"/>
-      <c r="L31" s="38" t="s">
-        <v>268</v>
-      </c>
-      <c r="M31" s="38" t="s">
-        <v>269</v>
-      </c>
-      <c r="N31" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O31" s="38" t="s">
-        <v>319</v>
-      </c>
-      <c r="P31" s="38" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q31" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="R31" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="S31" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="B32" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="37">
-        <v>1003001010</v>
-      </c>
-      <c r="F32" s="40" t="s">
-        <v>170</v>
-      </c>
-      <c r="G32" s="37">
-        <v>3203001010</v>
-      </c>
-      <c r="H32" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="I32" s="38" t="s">
-        <v>155</v>
-      </c>
-      <c r="J32" s="38" t="s">
-        <v>297</v>
-      </c>
-      <c r="K32" s="28"/>
-      <c r="L32" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="M32" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="N32" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="O32" s="38" t="s">
-        <v>320</v>
-      </c>
-      <c r="P32" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q32" s="42">
-        <v>46264.416666666664</v>
-      </c>
-      <c r="R32" s="42">
-        <v>46264.583333333336</v>
-      </c>
-      <c r="S32" s="38" t="s">
-        <v>273</v>
+      <c r="S32" s="9" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -5214,55 +5307,55 @@
   <dimension ref="A1:U28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" style="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" style="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.42578125" style="26" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8" style="26" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" style="26" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.42578125" style="26" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="28.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="11.42578125" style="26"/>
+    <col min="1" max="1" width="9.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" style="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8" style="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" style="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" style="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="11.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="11.42578125" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="J1" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="T1" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="U1" s="12"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="J1" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="T1" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="U1" s="25"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>46</v>
@@ -5271,54 +5364,54 @@
         <v>45</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="G2" s="6" t="s">
+      <c r="J2" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="L2" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="J2" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="K2" s="13" t="s">
+      <c r="M2" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q2" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="L2" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="O2" s="13" t="s">
+      <c r="R2" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="P2" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="R2" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="T2" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="U2" s="15" t="s">
-        <v>91</v>
+      <c r="T2" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="U2" s="13" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>63</v>
@@ -5327,25 +5420,25 @@
         <v>47</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E3" s="1">
         <v>1001001001</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="14" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="1">
         <v>3001001001</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>83</v>
@@ -5354,7 +5447,7 @@
         <v>78</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P3" s="1">
         <v>1003001001</v>
@@ -5363,10 +5456,10 @@
         <v>3203001001</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>4</v>
@@ -5374,7 +5467,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>64</v>
@@ -5383,25 +5476,25 @@
         <v>48</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E4" s="1">
         <v>1001001002</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="14" t="s">
         <v>7</v>
       </c>
       <c r="G4" s="1">
         <v>3001001002</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>84</v>
@@ -5410,7 +5503,7 @@
         <v>54</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P4" s="1">
         <v>1003001002</v>
@@ -5419,18 +5512,18 @@
         <v>3203001002</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>65</v>
@@ -5439,25 +5532,25 @@
         <v>49</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E5" s="1">
         <v>1001001003</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="14" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="1">
         <v>3001001003</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>72</v>
@@ -5466,7 +5559,7 @@
         <v>59</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P5" s="1">
         <v>1003001003</v>
@@ -5475,14 +5568,14 @@
         <v>3203001003</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="S5" s="18"/>
-      <c r="T5" s="18"/>
+        <v>161</v>
+      </c>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>66</v>
@@ -5491,25 +5584,25 @@
         <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E6" s="1">
         <v>1001001004</v>
       </c>
-      <c r="F6" s="16" t="s">
-        <v>174</v>
+      <c r="F6" s="14" t="s">
+        <v>172</v>
       </c>
       <c r="G6" s="1">
         <v>3001001004</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>63</v>
@@ -5518,7 +5611,7 @@
         <v>61</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P6" s="1">
         <v>1003001004</v>
@@ -5527,14 +5620,14 @@
         <v>3203001004</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="S6" s="18"/>
-      <c r="T6" s="18"/>
+        <v>162</v>
+      </c>
+      <c r="S6" s="15"/>
+      <c r="T6" s="15"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>67</v>
@@ -5543,25 +5636,25 @@
         <v>51</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E7" s="1">
         <v>1001001005</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="14" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="1">
         <v>3001001005</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>85</v>
@@ -5570,7 +5663,7 @@
         <v>52</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P7" s="1">
         <v>1003001005</v>
@@ -5579,12 +5672,12 @@
         <v>3203001005</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>68</v>
@@ -5593,25 +5686,25 @@
         <v>52</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E8" s="1">
         <v>1001001006</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="14" t="s">
         <v>12</v>
       </c>
       <c r="G8" s="1">
         <v>3001001006</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>86</v>
@@ -5620,7 +5713,7 @@
         <v>79</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P8" s="1">
         <v>1003001006</v>
@@ -5629,12 +5722,12 @@
         <v>3203001006</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>69</v>
@@ -5643,25 +5736,25 @@
         <v>53</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E9" s="1">
         <v>1001001007</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="14" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="1">
         <v>3001001007</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>87</v>
@@ -5670,7 +5763,7 @@
         <v>56</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P9" s="1">
         <v>1003001007</v>
@@ -5679,12 +5772,12 @@
         <v>3203001007</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>70</v>
@@ -5693,25 +5786,25 @@
         <v>54</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E10" s="1">
         <v>1001001008</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G10" s="1">
         <v>3001001008</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>71</v>
@@ -5720,7 +5813,7 @@
         <v>80</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P10" s="1">
         <v>1003001008</v>
@@ -5729,12 +5822,12 @@
         <v>3203001008</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>71</v>
@@ -5743,25 +5836,25 @@
         <v>55</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E11" s="1">
         <v>1001001009</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="14" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="1">
         <v>3001001009</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>88</v>
@@ -5770,7 +5863,7 @@
         <v>81</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P11" s="1">
         <v>1003001009</v>
@@ -5779,12 +5872,12 @@
         <v>3203001009</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>72</v>
@@ -5793,25 +5886,25 @@
         <v>56</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E12" s="1">
         <v>1001001010</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G12" s="1">
         <v>3001001010</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>89</v>
@@ -5820,7 +5913,7 @@
         <v>82</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P12" s="1">
         <v>1003001010</v>
@@ -5829,50 +5922,50 @@
         <v>3203001010</v>
       </c>
       <c r="R12" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="21"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="33"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="D15" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="F15" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>113</v>
-      </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
-        <v>180</v>
+      <c r="A16" s="16" t="s">
+        <v>178</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>73</v>
@@ -5881,7 +5974,7 @@
         <v>57</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E16" s="1">
         <v>1002001002</v>
@@ -5893,12 +5986,12 @@
         <v>3102001002</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
-        <v>181</v>
+      <c r="A17" s="16" t="s">
+        <v>179</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>74</v>
@@ -5907,7 +6000,7 @@
         <v>58</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E17" s="1">
         <v>1002001003</v>
@@ -5919,12 +6012,12 @@
         <v>3102001004</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
-        <v>182</v>
+      <c r="A18" s="16" t="s">
+        <v>180</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>75</v>
@@ -5933,24 +6026,24 @@
         <v>60</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E18" s="1">
         <v>1002001005</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G18" s="1">
         <v>3102001005</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="s">
-        <v>183</v>
+      <c r="A19" s="16" t="s">
+        <v>181</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>76</v>
@@ -5959,7 +6052,7 @@
         <v>61</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E19" s="1">
         <v>1002001007</v>
@@ -5971,12 +6064,12 @@
         <v>3102001008</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
-        <v>184</v>
+      <c r="A20" s="16" t="s">
+        <v>182</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>77</v>
@@ -5985,7 +6078,7 @@
         <v>62</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E20" s="1">
         <v>1002001009</v>
@@ -5997,147 +6090,147 @@
         <v>3102001009</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C22" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="25"/>
-      <c r="P22" s="18"/>
-      <c r="Q22" s="18"/>
+      <c r="C22" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="29"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C23" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" s="14" t="s">
+      <c r="C23" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="G23" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="P23" s="18"/>
-      <c r="Q23" s="18"/>
+      <c r="F23" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C24" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>171</v>
+        <v>173</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>169</v>
       </c>
       <c r="G24" s="1">
         <v>3104567821</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="P24" s="18"/>
-      <c r="Q24" s="18"/>
+        <v>117</v>
+      </c>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C25" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D25" s="2">
         <v>2</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>120</v>
+        <v>174</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>118</v>
       </c>
       <c r="G25" s="1">
         <v>3115678932</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="P25" s="18"/>
-      <c r="Q25" s="18"/>
+        <v>119</v>
+      </c>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="15"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C26" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D26" s="2">
         <v>2</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>172</v>
+        <v>175</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>170</v>
       </c>
       <c r="G26" s="1">
         <v>3126789043</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="P26" s="18"/>
-      <c r="Q26" s="18"/>
+        <v>120</v>
+      </c>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C27" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D27" s="2">
         <v>2</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>123</v>
+        <v>176</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>121</v>
       </c>
       <c r="G27" s="1">
         <v>3137890154</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C28" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D28" s="2">
         <v>2</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>173</v>
+        <v>177</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>171</v>
       </c>
       <c r="G28" s="1">
         <v>3148901265</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/2.DIAGRAMAS/PPP.xlsx
+++ b/2.DIAGRAMAS/PPP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aprendiz\Documents\ADSO, 2006\PROYECTO_ADSO_KJGA\2.DIAGRAMAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C1A8F4-D7C3-499C-BBE0-5F74F4993DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA2D77F-B0BC-41B5-814C-DBD22F3FAB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D1012828-DDFC-47C0-86DB-3A2BD43233B1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D1012828-DDFC-47C0-86DB-3A2BD43233B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Normal" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="418">
   <si>
     <t>Fundación</t>
   </si>
@@ -112,12 +112,6 @@
     <t>Huellas de Esperanza</t>
   </si>
   <si>
-    <t>Norte</t>
-  </si>
-  <si>
-    <t>Centro</t>
-  </si>
-  <si>
     <t>Andrea Castro</t>
   </si>
   <si>
@@ -130,15 +124,9 @@
     <t>Patitas Unidas</t>
   </si>
   <si>
-    <t>Oriente</t>
-  </si>
-  <si>
     <t>Felipe Navarro</t>
   </si>
   <si>
-    <t>Occidente</t>
-  </si>
-  <si>
     <t>Laura Salazar</t>
   </si>
   <si>
@@ -178,12 +166,6 @@
     <t>Marcela Duarte</t>
   </si>
   <si>
-    <t>apellidos</t>
-  </si>
-  <si>
-    <t>nombres</t>
-  </si>
-  <si>
     <t>Gomez</t>
   </si>
   <si>
@@ -376,9 +358,6 @@
     <t>doc_Fun</t>
   </si>
   <si>
-    <t>id_Fundacion</t>
-  </si>
-  <si>
     <t>FA001</t>
   </si>
   <si>
@@ -421,9 +400,6 @@
     <t>Fundacion</t>
   </si>
   <si>
-    <t>red_Social</t>
-  </si>
-  <si>
     <t>nom_Direc</t>
   </si>
   <si>
@@ -454,9 +430,6 @@
     <t>SF004</t>
   </si>
   <si>
-    <t>Sur</t>
-  </si>
-  <si>
     <t>SF005</t>
   </si>
   <si>
@@ -838,9 +811,6 @@
     <t>Descripción</t>
   </si>
   <si>
-    <t>Mascota perdida</t>
-  </si>
-  <si>
     <t>Perro</t>
   </si>
   <si>
@@ -1055,6 +1025,276 @@
   </si>
   <si>
     <t>tip_Public</t>
+  </si>
+  <si>
+    <t>perdida</t>
+  </si>
+  <si>
+    <t>id_Esp</t>
+  </si>
+  <si>
+    <t>ES001</t>
+  </si>
+  <si>
+    <t>ES002</t>
+  </si>
+  <si>
+    <t>Usaquen</t>
+  </si>
+  <si>
+    <t>Chapinero</t>
+  </si>
+  <si>
+    <t>Santa Fe</t>
+  </si>
+  <si>
+    <t>San Cristobal</t>
+  </si>
+  <si>
+    <t>Usme</t>
+  </si>
+  <si>
+    <t>Tunjuelito</t>
+  </si>
+  <si>
+    <t>Bosa</t>
+  </si>
+  <si>
+    <t>Kennedy</t>
+  </si>
+  <si>
+    <t>Fontibon</t>
+  </si>
+  <si>
+    <t>Engativa</t>
+  </si>
+  <si>
+    <t>Suba</t>
+  </si>
+  <si>
+    <t>Barrios Unidos</t>
+  </si>
+  <si>
+    <t>Teusaquillo</t>
+  </si>
+  <si>
+    <t>Los Martires</t>
+  </si>
+  <si>
+    <t>Antonio Narino</t>
+  </si>
+  <si>
+    <t>Puente Aranda</t>
+  </si>
+  <si>
+    <t>La Candelaria</t>
+  </si>
+  <si>
+    <t>Rafael Uribe Uribe</t>
+  </si>
+  <si>
+    <t>Ciudad Bolivar</t>
+  </si>
+  <si>
+    <t>Sumapaz</t>
+  </si>
+  <si>
+    <t>Barrios_Unidos</t>
+  </si>
+  <si>
+    <t>Los_Martires</t>
+  </si>
+  <si>
+    <t>Antonio_Narino</t>
+  </si>
+  <si>
+    <t>Puente_Aranda</t>
+  </si>
+  <si>
+    <t>La_Candelaria</t>
+  </si>
+  <si>
+    <t>Rafael_Uribe</t>
+  </si>
+  <si>
+    <t>Ciudad_Bolivar</t>
+  </si>
+  <si>
+    <t>Santa_Fe</t>
+  </si>
+  <si>
+    <t>San_Cristobal</t>
+  </si>
+  <si>
+    <t>id_Loc</t>
+  </si>
+  <si>
+    <t>Antonio_Nariño</t>
+  </si>
+  <si>
+    <t>Ciudad_Bolívar</t>
+  </si>
+  <si>
+    <t>Engativá</t>
+  </si>
+  <si>
+    <t>Fontibón</t>
+  </si>
+  <si>
+    <t>Los_Mártires</t>
+  </si>
+  <si>
+    <t>Rafael_Uribe_Uribe</t>
+  </si>
+  <si>
+    <t>San_Cristóbal</t>
+  </si>
+  <si>
+    <t>Usaquén</t>
+  </si>
+  <si>
+    <t>LC001</t>
+  </si>
+  <si>
+    <t>LC002</t>
+  </si>
+  <si>
+    <t>LC003</t>
+  </si>
+  <si>
+    <t>LC004</t>
+  </si>
+  <si>
+    <t>LC005</t>
+  </si>
+  <si>
+    <t>LC006</t>
+  </si>
+  <si>
+    <t>LC007</t>
+  </si>
+  <si>
+    <t>LC008</t>
+  </si>
+  <si>
+    <t>LC009</t>
+  </si>
+  <si>
+    <t>LC010</t>
+  </si>
+  <si>
+    <t>LC011</t>
+  </si>
+  <si>
+    <t>LC012</t>
+  </si>
+  <si>
+    <t>LC013</t>
+  </si>
+  <si>
+    <t>LC014</t>
+  </si>
+  <si>
+    <t>LC015</t>
+  </si>
+  <si>
+    <t>LC016</t>
+  </si>
+  <si>
+    <t>LC017</t>
+  </si>
+  <si>
+    <t>LC018</t>
+  </si>
+  <si>
+    <t>LC019</t>
+  </si>
+  <si>
+    <t>LC020</t>
+  </si>
+  <si>
+    <t>red_Soc</t>
+  </si>
+  <si>
+    <t>nit</t>
+  </si>
+  <si>
+    <t>901100100-1</t>
+  </si>
+  <si>
+    <t>901200200-2</t>
+  </si>
+  <si>
+    <t>901300300-3</t>
+  </si>
+  <si>
+    <t>901400400-4</t>
+  </si>
+  <si>
+    <t>901500500-5</t>
+  </si>
+  <si>
+    <t>Ave</t>
+  </si>
+  <si>
+    <t>Conejo</t>
+  </si>
+  <si>
+    <t>Hámster</t>
+  </si>
+  <si>
+    <t>Cobayo</t>
+  </si>
+  <si>
+    <t>Tortuga</t>
+  </si>
+  <si>
+    <t>Hurón</t>
+  </si>
+  <si>
+    <t>ES003</t>
+  </si>
+  <si>
+    <t>ES004</t>
+  </si>
+  <si>
+    <t>ES005</t>
+  </si>
+  <si>
+    <t>ES006</t>
+  </si>
+  <si>
+    <t>ES007</t>
+  </si>
+  <si>
+    <t>ES008</t>
+  </si>
+  <si>
+    <t>id_Ep</t>
+  </si>
+  <si>
+    <t>tip_Ep</t>
+  </si>
+  <si>
+    <t>EP001</t>
+  </si>
+  <si>
+    <t>EP002</t>
+  </si>
+  <si>
+    <t>EP003</t>
+  </si>
+  <si>
+    <t>EP004</t>
+  </si>
+  <si>
+    <t>EP005</t>
+  </si>
+  <si>
+    <t>EP006</t>
+  </si>
+  <si>
+    <t>EP007</t>
   </si>
 </sst>
 </file>
@@ -1139,12 +1379,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="Times New Roman"/>
@@ -1171,6 +1405,14 @@
       <color theme="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1225,7 +1467,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1305,6 +1547,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1318,7 +1571,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1354,23 +1607,14 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="9" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1381,29 +1625,26 @@
     <xf numFmtId="22" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="9" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1417,35 +1658,50 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -1790,7 +2046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53CAFCBD-51ED-4D7F-B584-3F5A2EED76BE}">
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -1798,100 +2054,106 @@
     <col min="3" max="3" width="27.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+    </row>
+    <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>247</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>322</v>
+      </c>
+      <c r="J2" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="K2" s="39" t="s">
+        <v>250</v>
+      </c>
+      <c r="L2" s="39" t="s">
+        <v>251</v>
+      </c>
+      <c r="M2" s="39" t="s">
+        <v>252</v>
+      </c>
+      <c r="N2" s="39" t="s">
+        <v>253</v>
+      </c>
+      <c r="O2" s="40" t="s">
+        <v>254</v>
+      </c>
+      <c r="P2" s="40" t="s">
         <v>255</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-    </row>
-    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="I2" s="43" t="s">
-        <v>332</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="K2" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="L2" s="18" t="s">
-        <v>260</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>261</v>
-      </c>
-      <c r="N2" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="O2" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="P2" s="22" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q2" s="40" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>6</v>
@@ -1900,25 +2162,25 @@
         <v>6</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>23</v>
+        <v>332</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="N3" s="8" t="s">
         <v>6</v>
@@ -1927,21 +2189,24 @@
         <v>6</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>6</v>
@@ -1950,26 +2215,26 @@
         <v>6</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="N4" s="8" t="s">
         <v>6</v>
       </c>
@@ -1977,21 +2242,24 @@
         <v>6</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>6</v>
@@ -2000,25 +2268,25 @@
         <v>6</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>29</v>
+        <v>334</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="N5" s="8" t="s">
         <v>6</v>
@@ -2027,21 +2295,24 @@
         <v>6</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>6</v>
@@ -2050,25 +2321,25 @@
         <v>6</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>31</v>
+        <v>335</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="N6" s="8" t="s">
         <v>6</v>
@@ -2077,21 +2348,24 @@
         <v>6</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>6</v>
@@ -2100,26 +2374,26 @@
         <v>6</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="N7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2127,10 +2401,13 @@
         <v>6</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>3</v>
       </c>
@@ -2138,10 +2415,10 @@
         <v>11</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>6</v>
@@ -2150,25 +2427,25 @@
         <v>6</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="K8" s="1" t="s">
-        <v>23</v>
+        <v>337</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>6</v>
@@ -2177,21 +2454,24 @@
         <v>6</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>6</v>
@@ -2200,25 +2480,25 @@
         <v>6</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>24</v>
+        <v>338</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="N9" s="8" t="s">
         <v>6</v>
@@ -2227,10 +2507,13 @@
         <v>6</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>3</v>
       </c>
@@ -2238,10 +2521,10 @@
         <v>14</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>6</v>
@@ -2250,26 +2533,26 @@
         <v>6</v>
       </c>
       <c r="G10" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="M10" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="N10" s="8" t="s">
         <v>6</v>
       </c>
@@ -2277,10 +2560,13 @@
         <v>6</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>3</v>
       </c>
@@ -2288,10 +2574,10 @@
         <v>16</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>6</v>
@@ -2300,25 +2586,25 @@
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>31</v>
+        <v>340</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="N11" s="8" t="s">
         <v>6</v>
@@ -2327,10 +2613,13 @@
         <v>6</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>3</v>
       </c>
@@ -2338,10 +2627,10 @@
         <v>18</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>6</v>
@@ -2350,25 +2639,25 @@
         <v>6</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>137</v>
+        <v>341</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="N12" s="8" t="s">
         <v>6</v>
@@ -2377,48 +2666,51 @@
         <v>6</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>23</v>
+        <v>342</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="N13" s="8" t="s">
         <v>6</v>
@@ -2427,962 +2719,1022 @@
         <v>6</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q13" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>24</v>
+        <v>343</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="N14" s="20">
+        <v>287</v>
+      </c>
+      <c r="N14" s="17">
         <v>46280.375</v>
       </c>
-      <c r="O14" s="21">
+      <c r="O14" s="18">
         <v>46280.541666666664</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="F15" s="10" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>29</v>
+        <v>344</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q15" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="F16" s="10" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>31</v>
+        <v>345</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="N16" s="20">
+        <v>291</v>
+      </c>
+      <c r="N16" s="17">
         <v>46254.416666666664</v>
       </c>
-      <c r="O16" s="21">
+      <c r="O16" s="18">
         <v>46254.583333333336</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q16" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="M17" s="1" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q17" s="9" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>23</v>
+        <v>347</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="N18" s="20">
+        <v>294</v>
+      </c>
+      <c r="N18" s="17">
         <v>46275.333333333336</v>
       </c>
-      <c r="O18" s="21">
+      <c r="O18" s="18">
         <v>46275.5</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q18" s="9" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>24</v>
+        <v>348</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q19" s="9" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>29</v>
+        <v>349</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="N20" s="20">
+        <v>287</v>
+      </c>
+      <c r="N20" s="17">
         <v>46283.458333333336</v>
       </c>
-      <c r="O20" s="21">
+      <c r="O20" s="18">
         <v>46283.625</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q20" s="9" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>31</v>
+        <v>350</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q21" s="9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>137</v>
+        <v>351</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="N22" s="21">
+        <v>291</v>
+      </c>
+      <c r="N22" s="18">
         <v>46259.375</v>
       </c>
-      <c r="O22" s="21">
+      <c r="O22" s="18">
         <v>46259.541666666664</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>23</v>
+        <v>342</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q23" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>24</v>
+        <v>343</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="N24" s="20">
+        <v>287</v>
+      </c>
+      <c r="N24" s="17">
         <v>46280.375</v>
       </c>
-      <c r="O24" s="21">
+      <c r="O24" s="18">
         <v>46280.541666666664</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q24" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>29</v>
+        <v>344</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q25" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>31</v>
+        <v>345</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="N26" s="20">
+        <v>291</v>
+      </c>
+      <c r="N26" s="17">
         <v>46254.416666666664</v>
       </c>
-      <c r="O26" s="21">
+      <c r="O26" s="18">
         <v>46254.583333333336</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q26" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="G27" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="M27" s="1" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q27" s="9" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>23</v>
+        <v>347</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="N28" s="20">
+        <v>294</v>
+      </c>
+      <c r="N28" s="17">
         <v>46275.333333333336</v>
       </c>
-      <c r="O28" s="21">
+      <c r="O28" s="18">
         <v>46275.5</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q28" s="9" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>24</v>
+        <v>348</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q29" s="9" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>29</v>
+        <v>349</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="N30" s="20">
+        <v>287</v>
+      </c>
+      <c r="N30" s="17">
         <v>46283.458333333336</v>
       </c>
-      <c r="O30" s="21">
+      <c r="O30" s="18">
         <v>46283.625</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q30" s="9" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>31</v>
+        <v>350</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="Q31" s="9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>137</v>
+        <v>351</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="N32" s="21">
+        <v>291</v>
+      </c>
+      <c r="N32" s="18">
         <v>46259.375</v>
       </c>
-      <c r="O32" s="21">
+      <c r="O32" s="18">
         <v>46259.541666666664</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>271</v>
+        <v>261</v>
+      </c>
+      <c r="Q32" s="9" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3390,120 +3742,126 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CC2C4B9-5300-4C27-836E-2A9C35E8924B}">
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:T32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="6.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="11.42578125" style="3"/>
+    <col min="20" max="20" width="10.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-    </row>
-    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="B2" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="D2" s="36" t="s">
-        <v>333</v>
-      </c>
-      <c r="E2" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="F2" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="G2" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="H2" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="I2" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="J2" s="38" t="s">
-        <v>337</v>
-      </c>
-      <c r="K2" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="L2" s="38" t="s">
-        <v>309</v>
-      </c>
-      <c r="M2" s="38" t="s">
-        <v>310</v>
-      </c>
-      <c r="N2" s="38" t="s">
-        <v>311</v>
-      </c>
-      <c r="O2" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="P2" s="39" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q2" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="R2" s="39" t="s">
-        <v>315</v>
-      </c>
-      <c r="S2" s="39" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+    </row>
+    <row r="2" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="L2" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="M2" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="N2" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="O2" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="P2" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q2" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="R2" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="S2" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="T2" s="22" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>4</v>
@@ -3518,51 +3876,54 @@
         <v>3001001001</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>6</v>
+        <v>332</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>266</v>
+        <v>6</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>23</v>
+        <v>257</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>4</v>
@@ -3577,51 +3938,54 @@
         <v>3001001002</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>6</v>
+        <v>333</v>
       </c>
       <c r="I4" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="P4" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="K4" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>275</v>
-      </c>
       <c r="Q4" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R4" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>4</v>
@@ -3636,51 +4000,54 @@
         <v>3001001003</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>6</v>
+        <v>359</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="L5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="N5" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="M5" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="O5" s="8" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="P5" s="9" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R5" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S5" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T5" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>4</v>
@@ -3695,51 +4062,54 @@
         <v>3001001004</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>6</v>
+        <v>360</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>272</v>
+        <v>6</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>310</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>31</v>
+        <v>268</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="P6" s="9" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R6" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S6" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T6" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>4</v>
@@ -3754,51 +4124,54 @@
         <v>3001001005</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>6</v>
+        <v>336</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="P7" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="K7" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>275</v>
-      </c>
       <c r="Q7" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S7" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T7" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>4</v>
@@ -3813,51 +4186,54 @@
         <v>3001001006</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>6</v>
+        <v>337</v>
       </c>
       <c r="I8" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="L8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="N8" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="M8" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>23</v>
-      </c>
       <c r="O8" s="8" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="P8" s="9" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R8" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S8" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T8" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>4</v>
@@ -3872,51 +4248,54 @@
         <v>3001001007</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>6</v>
+        <v>338</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>266</v>
+        <v>6</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>313</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>24</v>
+        <v>274</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="P9" s="9" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R9" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S9" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T9" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>4</v>
@@ -3931,51 +4310,54 @@
         <v>3001001008</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>6</v>
+        <v>339</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="P10" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="K10" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>275</v>
-      </c>
       <c r="Q10" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R10" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S10" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T10" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>4</v>
@@ -3990,51 +4372,54 @@
         <v>3001001009</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>6</v>
+        <v>340</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>266</v>
+        <v>6</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>315</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>31</v>
+        <v>278</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R11" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S11" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T11" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>4</v>
@@ -4049,51 +4434,54 @@
         <v>3001001010</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>6</v>
+        <v>341</v>
       </c>
       <c r="I12" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>272</v>
+        <v>6</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>316</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>290</v>
+        <v>262</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>137</v>
+        <v>280</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="P12" s="9" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R12" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S12" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T12" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>4</v>
@@ -4101,58 +4489,61 @@
       <c r="E13" s="8">
         <v>1002001001</v>
       </c>
-      <c r="F13" s="40" t="s">
+      <c r="F13" s="23" t="s">
         <v>21</v>
       </c>
       <c r="G13" s="8">
         <v>3102001001</v>
       </c>
-      <c r="H13" s="9" t="s">
-        <v>173</v>
+      <c r="H13" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>266</v>
+        <v>164</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>317</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="O13" s="40" t="s">
-        <v>293</v>
+        <v>257</v>
+      </c>
+      <c r="O13" s="23" t="s">
+        <v>283</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R13" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T13" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>4</v>
@@ -4160,58 +4551,61 @@
       <c r="E14" s="8">
         <v>1002001001</v>
       </c>
-      <c r="F14" s="40" t="s">
+      <c r="F14" s="23" t="s">
         <v>21</v>
       </c>
       <c r="G14" s="8">
         <v>3102001001</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>173</v>
+      <c r="H14" s="8" t="s">
+        <v>352</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>295</v>
+        <v>164</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="O14" s="40" t="s">
-        <v>296</v>
+        <v>260</v>
+      </c>
+      <c r="O14" s="23" t="s">
+        <v>286</v>
       </c>
       <c r="P14" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q14" s="41">
+        <v>287</v>
+      </c>
+      <c r="Q14" s="24">
         <v>46280.375</v>
       </c>
-      <c r="R14" s="41">
+      <c r="R14" s="24">
         <v>46280.541666666664</v>
       </c>
       <c r="S14" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T14" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>4</v>
@@ -4219,58 +4613,61 @@
       <c r="E15" s="8">
         <v>1002001003</v>
       </c>
-      <c r="F15" s="40" t="s">
-        <v>27</v>
+      <c r="F15" s="23" t="s">
+        <v>25</v>
       </c>
       <c r="G15" s="8">
         <v>3102001003</v>
       </c>
-      <c r="H15" s="9" t="s">
-        <v>174</v>
+      <c r="H15" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>272</v>
+        <v>165</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>318</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O15" s="40" t="s">
-        <v>298</v>
+        <v>263</v>
+      </c>
+      <c r="O15" s="23" t="s">
+        <v>288</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R15" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S15" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T15" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>4</v>
@@ -4278,58 +4675,61 @@
       <c r="E16" s="8">
         <v>1002001003</v>
       </c>
-      <c r="F16" s="40" t="s">
-        <v>27</v>
+      <c r="F16" s="23" t="s">
+        <v>25</v>
       </c>
       <c r="G16" s="8">
         <v>3102001003</v>
       </c>
-      <c r="H16" s="9" t="s">
-        <v>174</v>
+      <c r="H16" s="8" t="s">
+        <v>353</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>295</v>
+        <v>165</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>138</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="O16" s="40" t="s">
-        <v>300</v>
+        <v>260</v>
+      </c>
+      <c r="O16" s="23" t="s">
+        <v>290</v>
       </c>
       <c r="P16" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q16" s="41">
+        <v>291</v>
+      </c>
+      <c r="Q16" s="24">
         <v>46254.416666666664</v>
       </c>
-      <c r="R16" s="41">
+      <c r="R16" s="24">
         <v>46254.583333333336</v>
       </c>
       <c r="S16" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T16" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>4</v>
@@ -4337,58 +4737,61 @@
       <c r="E17" s="8">
         <v>1002001005</v>
       </c>
-      <c r="F17" s="40" t="s">
-        <v>184</v>
+      <c r="F17" s="23" t="s">
+        <v>175</v>
       </c>
       <c r="G17" s="8">
         <v>3102001005</v>
       </c>
-      <c r="H17" s="9" t="s">
-        <v>175</v>
+      <c r="H17" s="8" t="s">
+        <v>354</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="J17" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="O17" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="K17" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="N17" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="O17" s="40" t="s">
-        <v>302</v>
-      </c>
       <c r="P17" s="9" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R17" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S17" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T17" s="9" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>4</v>
@@ -4396,58 +4799,61 @@
       <c r="E18" s="8">
         <v>1002001005</v>
       </c>
-      <c r="F18" s="40" t="s">
-        <v>184</v>
+      <c r="F18" s="23" t="s">
+        <v>175</v>
       </c>
       <c r="G18" s="8">
         <v>3102001005</v>
       </c>
-      <c r="H18" s="9" t="s">
-        <v>175</v>
+      <c r="H18" s="8" t="s">
+        <v>355</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>295</v>
+        <v>166</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>140</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="O18" s="40" t="s">
-        <v>303</v>
+        <v>260</v>
+      </c>
+      <c r="O18" s="23" t="s">
+        <v>293</v>
       </c>
       <c r="P18" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q18" s="41">
+        <v>294</v>
+      </c>
+      <c r="Q18" s="24">
         <v>46275.333333333336</v>
       </c>
-      <c r="R18" s="41">
+      <c r="R18" s="24">
         <v>46275.5</v>
       </c>
       <c r="S18" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T18" s="9" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>4</v>
@@ -4455,58 +4861,61 @@
       <c r="E19" s="8">
         <v>1002001007</v>
       </c>
-      <c r="F19" s="40" t="s">
-        <v>38</v>
+      <c r="F19" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="G19" s="8">
         <v>3102001007</v>
       </c>
-      <c r="H19" s="9" t="s">
-        <v>176</v>
+      <c r="H19" s="8" t="s">
+        <v>356</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>272</v>
+        <v>167</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>320</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="O19" s="40" t="s">
-        <v>305</v>
+        <v>268</v>
+      </c>
+      <c r="O19" s="23" t="s">
+        <v>295</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R19" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T19" s="9" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>4</v>
@@ -4514,58 +4923,61 @@
       <c r="E20" s="8">
         <v>1002001007</v>
       </c>
-      <c r="F20" s="40" t="s">
-        <v>38</v>
+      <c r="F20" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="G20" s="8">
         <v>3102001007</v>
       </c>
-      <c r="H20" s="9" t="s">
-        <v>176</v>
+      <c r="H20" s="8" t="s">
+        <v>357</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>295</v>
+        <v>167</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>142</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O20" s="40" t="s">
-        <v>306</v>
+        <v>260</v>
+      </c>
+      <c r="O20" s="23" t="s">
+        <v>296</v>
       </c>
       <c r="P20" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q20" s="41">
+        <v>287</v>
+      </c>
+      <c r="Q20" s="24">
         <v>46283.458333333336</v>
       </c>
-      <c r="R20" s="41">
+      <c r="R20" s="24">
         <v>46283.625</v>
       </c>
       <c r="S20" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T20" s="9" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>4</v>
@@ -4573,58 +4985,61 @@
       <c r="E21" s="8">
         <v>1002001009</v>
       </c>
-      <c r="F21" s="40" t="s">
-        <v>41</v>
+      <c r="F21" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="G21" s="8">
         <v>3102001009</v>
       </c>
-      <c r="H21" s="9" t="s">
-        <v>177</v>
+      <c r="H21" s="8" t="s">
+        <v>358</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>266</v>
+        <v>168</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>321</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="O21" s="40" t="s">
-        <v>307</v>
+        <v>270</v>
+      </c>
+      <c r="O21" s="23" t="s">
+        <v>297</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R21" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S21" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="T21" s="9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>4</v>
@@ -4632,58 +5047,61 @@
       <c r="E22" s="8">
         <v>1002001009</v>
       </c>
-      <c r="F22" s="40" t="s">
-        <v>41</v>
+      <c r="F22" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="G22" s="8">
         <v>3102001009</v>
       </c>
-      <c r="H22" s="9" t="s">
-        <v>177</v>
+      <c r="H22" s="8" t="s">
+        <v>351</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>295</v>
+        <v>168</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="N22" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="O22" s="40" t="s">
-        <v>308</v>
+        <v>260</v>
+      </c>
+      <c r="O22" s="23" t="s">
+        <v>298</v>
       </c>
       <c r="P22" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q22" s="41">
+        <v>291</v>
+      </c>
+      <c r="Q22" s="24">
         <v>46259.375</v>
       </c>
-      <c r="R22" s="41">
+      <c r="R22" s="24">
         <v>46259.541666666664</v>
       </c>
       <c r="S22" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="T22" s="9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>4</v>
@@ -4691,58 +5109,61 @@
       <c r="E23" s="8">
         <v>1003001001</v>
       </c>
-      <c r="F23" s="40" t="s">
-        <v>159</v>
+      <c r="F23" s="23" t="s">
+        <v>150</v>
       </c>
       <c r="G23" s="8">
         <v>3203001001</v>
       </c>
-      <c r="H23" s="9" t="s">
-        <v>173</v>
+      <c r="H23" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>266</v>
+        <v>164</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>317</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="O23" s="40" t="s">
-        <v>293</v>
+        <v>257</v>
+      </c>
+      <c r="O23" s="23" t="s">
+        <v>283</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R23" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S23" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="T23" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>4</v>
@@ -4750,58 +5171,61 @@
       <c r="E24" s="8">
         <v>1003001002</v>
       </c>
-      <c r="F24" s="40" t="s">
-        <v>160</v>
+      <c r="F24" s="23" t="s">
+        <v>151</v>
       </c>
       <c r="G24" s="8">
         <v>3203001002</v>
       </c>
-      <c r="H24" s="9" t="s">
-        <v>173</v>
+      <c r="H24" s="8" t="s">
+        <v>352</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>295</v>
+        <v>164</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="O24" s="40" t="s">
-        <v>296</v>
+        <v>260</v>
+      </c>
+      <c r="O24" s="23" t="s">
+        <v>286</v>
       </c>
       <c r="P24" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q24" s="41">
+        <v>287</v>
+      </c>
+      <c r="Q24" s="24">
         <v>46280.375</v>
       </c>
-      <c r="R24" s="41">
+      <c r="R24" s="24">
         <v>46280.541666666664</v>
       </c>
       <c r="S24" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="T24" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A25" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>4</v>
@@ -4809,58 +5233,61 @@
       <c r="E25" s="8">
         <v>1003001003</v>
       </c>
-      <c r="F25" s="40" t="s">
-        <v>161</v>
+      <c r="F25" s="23" t="s">
+        <v>152</v>
       </c>
       <c r="G25" s="8">
         <v>3203001003</v>
       </c>
-      <c r="H25" s="9" t="s">
-        <v>174</v>
+      <c r="H25" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>272</v>
+        <v>165</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>318</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O25" s="40" t="s">
-        <v>298</v>
+        <v>263</v>
+      </c>
+      <c r="O25" s="23" t="s">
+        <v>288</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R25" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S25" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="T25" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>4</v>
@@ -4868,58 +5295,61 @@
       <c r="E26" s="8">
         <v>1003001004</v>
       </c>
-      <c r="F26" s="40" t="s">
-        <v>162</v>
+      <c r="F26" s="23" t="s">
+        <v>153</v>
       </c>
       <c r="G26" s="8">
         <v>3203001004</v>
       </c>
-      <c r="H26" s="9" t="s">
-        <v>174</v>
+      <c r="H26" s="8" t="s">
+        <v>353</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>295</v>
+        <v>165</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>138</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="O26" s="40" t="s">
-        <v>300</v>
+        <v>260</v>
+      </c>
+      <c r="O26" s="23" t="s">
+        <v>290</v>
       </c>
       <c r="P26" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q26" s="41">
+        <v>291</v>
+      </c>
+      <c r="Q26" s="24">
         <v>46254.416666666664</v>
       </c>
-      <c r="R26" s="41">
+      <c r="R26" s="24">
         <v>46254.583333333336</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="T26" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>4</v>
@@ -4927,58 +5357,61 @@
       <c r="E27" s="8">
         <v>1003001005</v>
       </c>
-      <c r="F27" s="40" t="s">
-        <v>163</v>
+      <c r="F27" s="23" t="s">
+        <v>154</v>
       </c>
       <c r="G27" s="8">
         <v>3203001005</v>
       </c>
-      <c r="H27" s="9" t="s">
-        <v>175</v>
+      <c r="H27" s="8" t="s">
+        <v>354</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="J27" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="O27" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="K27" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="M27" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="O27" s="40" t="s">
-        <v>302</v>
-      </c>
       <c r="P27" s="9" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R27" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S27" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="T27" s="9" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>4</v>
@@ -4986,58 +5419,61 @@
       <c r="E28" s="8">
         <v>1003001006</v>
       </c>
-      <c r="F28" s="40" t="s">
-        <v>164</v>
+      <c r="F28" s="23" t="s">
+        <v>155</v>
       </c>
       <c r="G28" s="8">
         <v>3203001006</v>
       </c>
-      <c r="H28" s="9" t="s">
-        <v>175</v>
+      <c r="H28" s="8" t="s">
+        <v>355</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>295</v>
+        <v>166</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>140</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="N28" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="O28" s="40" t="s">
-        <v>303</v>
+        <v>260</v>
+      </c>
+      <c r="O28" s="23" t="s">
+        <v>293</v>
       </c>
       <c r="P28" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q28" s="41">
+        <v>294</v>
+      </c>
+      <c r="Q28" s="24">
         <v>46275.333333333336</v>
       </c>
-      <c r="R28" s="41">
+      <c r="R28" s="24">
         <v>46275.5</v>
       </c>
       <c r="S28" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="T28" s="9" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>4</v>
@@ -5045,58 +5481,61 @@
       <c r="E29" s="8">
         <v>1003001007</v>
       </c>
-      <c r="F29" s="40" t="s">
-        <v>165</v>
+      <c r="F29" s="23" t="s">
+        <v>156</v>
       </c>
       <c r="G29" s="8">
         <v>3203001007</v>
       </c>
-      <c r="H29" s="9" t="s">
-        <v>176</v>
+      <c r="H29" s="8" t="s">
+        <v>356</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>272</v>
+        <v>167</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>320</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="O29" s="40" t="s">
-        <v>305</v>
+        <v>268</v>
+      </c>
+      <c r="O29" s="23" t="s">
+        <v>295</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R29" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S29" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="T29" s="9" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>4</v>
@@ -5104,58 +5543,61 @@
       <c r="E30" s="8">
         <v>1003001008</v>
       </c>
-      <c r="F30" s="40" t="s">
-        <v>166</v>
+      <c r="F30" s="23" t="s">
+        <v>157</v>
       </c>
       <c r="G30" s="8">
         <v>3203001008</v>
       </c>
-      <c r="H30" s="9" t="s">
-        <v>176</v>
+      <c r="H30" s="8" t="s">
+        <v>357</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>295</v>
+        <v>167</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>142</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="N30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O30" s="40" t="s">
-        <v>306</v>
+        <v>260</v>
+      </c>
+      <c r="O30" s="23" t="s">
+        <v>296</v>
       </c>
       <c r="P30" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q30" s="41">
+        <v>287</v>
+      </c>
+      <c r="Q30" s="24">
         <v>46283.458333333336</v>
       </c>
-      <c r="R30" s="41">
+      <c r="R30" s="24">
         <v>46283.625</v>
       </c>
       <c r="S30" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="T30" s="9" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>4</v>
@@ -5163,58 +5605,61 @@
       <c r="E31" s="8">
         <v>1003001009</v>
       </c>
-      <c r="F31" s="40" t="s">
-        <v>167</v>
+      <c r="F31" s="23" t="s">
+        <v>158</v>
       </c>
       <c r="G31" s="8">
         <v>3203001009</v>
       </c>
-      <c r="H31" s="9" t="s">
-        <v>177</v>
+      <c r="H31" s="8" t="s">
+        <v>358</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>266</v>
+        <v>168</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>321</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="O31" s="40" t="s">
-        <v>307</v>
+        <v>270</v>
+      </c>
+      <c r="O31" s="23" t="s">
+        <v>297</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R31" s="9" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S31" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="T31" s="9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>4</v>
@@ -5222,52 +5667,55 @@
       <c r="E32" s="8">
         <v>1003001010</v>
       </c>
-      <c r="F32" s="40" t="s">
-        <v>168</v>
+      <c r="F32" s="23" t="s">
+        <v>159</v>
       </c>
       <c r="G32" s="8">
         <v>3203001010</v>
       </c>
-      <c r="H32" s="9" t="s">
-        <v>177</v>
+      <c r="H32" s="8" t="s">
+        <v>351</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>295</v>
+        <v>168</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="N32" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="O32" s="40" t="s">
-        <v>308</v>
+        <v>260</v>
+      </c>
+      <c r="O32" s="23" t="s">
+        <v>298</v>
       </c>
       <c r="P32" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q32" s="41">
+        <v>291</v>
+      </c>
+      <c r="Q32" s="24">
         <v>46259.375</v>
       </c>
-      <c r="R32" s="41">
+      <c r="R32" s="24">
         <v>46259.541666666664</v>
       </c>
       <c r="S32" s="9" t="s">
-        <v>271</v>
+        <v>261</v>
+      </c>
+      <c r="T32" s="9" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:T1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F3" r:id="rId1" display="mailto:laura.gomez@correo.com" xr:uid="{4AF90779-ABB9-4953-AAF8-146090EC2F71}"/>
@@ -5304,677 +5752,835 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CCA6FB2-786D-496D-89D1-941A006DE469}">
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:W48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8" style="17" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" style="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="11.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="28.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="11.42578125" style="17"/>
+    <col min="1" max="1" width="11.7109375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="15" customWidth="1"/>
+    <col min="8" max="8" width="26.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" style="15" customWidth="1"/>
+    <col min="12" max="12" width="11" style="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="15" customWidth="1"/>
+    <col min="17" max="17" width="10.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="15" customWidth="1"/>
+    <col min="20" max="20" width="34.5703125" style="15" customWidth="1"/>
+    <col min="21" max="21" width="7.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.7109375" style="15" customWidth="1"/>
+    <col min="23" max="23" width="20" style="15" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.7109375" style="15" customWidth="1"/>
+    <col min="25" max="25" width="20" style="15" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20" style="15" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="11.42578125" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="J1" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="T1" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="U1" s="25"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1"/>
+      <c r="K1" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="35"/>
+      <c r="V1" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="W1" s="30"/>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>46</v>
+        <v>324</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>45</v>
+        <v>325</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F2" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="I2"/>
+      <c r="K2" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="T2" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="V2" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="W2" s="31" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="P2" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q2" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="R2" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="T2" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="U2" s="13" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="B3" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E3" s="1">
         <v>1001001001</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="13" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="1">
         <v>3001001001</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="P3" s="1">
+      <c r="H3" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I3"/>
+      <c r="K3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="R3" s="1">
         <v>1003001001</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="S3" s="1">
         <v>3203001001</v>
       </c>
-      <c r="R3" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="U3" s="2" t="s">
+      <c r="T3" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="W3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E4" s="1">
         <v>1001001002</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>7</v>
       </c>
       <c r="G4" s="1">
         <v>3001001002</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="P4" s="1">
+      <c r="H4" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="I4"/>
+      <c r="K4" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="R4" s="1">
         <v>1003001002</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="S4" s="1">
         <v>3203001002</v>
       </c>
-      <c r="R4" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T4" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E5" s="1">
         <v>1001001003</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="1">
         <v>3001001003</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="P5" s="1">
+      <c r="H5" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I5"/>
+      <c r="K5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="R5" s="1">
         <v>1003001003</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="S5" s="1">
         <v>3203001003</v>
       </c>
-      <c r="R5" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T5" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E6" s="1">
         <v>1001001004</v>
       </c>
-      <c r="F6" s="14" t="s">
-        <v>172</v>
+      <c r="F6" s="13" t="s">
+        <v>163</v>
       </c>
       <c r="G6" s="1">
         <v>3001001004</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="L6" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="I6"/>
+      <c r="K6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q6" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="N6" s="1" t="s">
+      <c r="R6" s="1">
+        <v>1003001004</v>
+      </c>
+      <c r="S6" s="1">
+        <v>3203001004</v>
+      </c>
+      <c r="T6" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="V6" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="W6" s="30"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="P6" s="1">
-        <v>1003001004</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>3203001004</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E7" s="1">
         <v>1001001005</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="13" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="1">
         <v>3001001005</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="P7" s="1">
+      <c r="H7" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="I7"/>
+      <c r="K7" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="R7" s="1">
         <v>1003001005</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="S7" s="1">
         <v>3203001005</v>
       </c>
-      <c r="R7" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T7" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="V7" s="31" t="s">
+        <v>409</v>
+      </c>
+      <c r="W7" s="31" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E8" s="1">
         <v>1001001006</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="13" t="s">
         <v>12</v>
       </c>
       <c r="G8" s="1">
         <v>3001001006</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="P8" s="1">
+      <c r="H8" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="I8"/>
+      <c r="K8" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="R8" s="1">
         <v>1003001006</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="S8" s="1">
         <v>3203001006</v>
       </c>
-      <c r="R8" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T8" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E9" s="1">
         <v>1001001007</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="1">
         <v>3001001007</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="O9" s="2" t="s">
+      <c r="H9" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="I9"/>
+      <c r="K9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="R9" s="1">
+        <v>1003001007</v>
+      </c>
+      <c r="S9" s="1">
+        <v>3203001007</v>
+      </c>
+      <c r="T9" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="P9" s="1">
-        <v>1003001007</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>3203001007</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V9" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E10" s="1">
         <v>1001001008</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="13" t="s">
         <v>15</v>
       </c>
       <c r="G10" s="1">
         <v>3001001008</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="P10" s="1">
+      <c r="H10" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="I10"/>
+      <c r="K10" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="R10" s="1">
         <v>1003001008</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="S10" s="1">
         <v>3203001008</v>
       </c>
-      <c r="R10" s="5" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T10" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E11" s="1">
         <v>1001001009</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="1">
         <v>3001001009</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="P11" s="1">
+      <c r="H11" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="I11"/>
+      <c r="K11" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="R11" s="1">
         <v>1003001009</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="S11" s="1">
         <v>3203001009</v>
       </c>
-      <c r="R11" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T11" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E12" s="1">
         <v>1001001010</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="13" t="s">
         <v>19</v>
       </c>
       <c r="G12" s="1">
         <v>3001001010</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="P12" s="1">
+      <c r="H12" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="I12"/>
+      <c r="K12" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="R12" s="1">
         <v>1003001010</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="S12" s="1">
         <v>3203001010</v>
       </c>
-      <c r="R12" s="5" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+      <c r="T12" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V13" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="33"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="29"/>
+      <c r="V14" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>178</v>
+        <v>121</v>
+      </c>
+      <c r="K15" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="L15" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="M15" s="44" t="s">
+        <v>300</v>
+      </c>
+      <c r="N15" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="O15" s="33" t="s">
+        <v>409</v>
+      </c>
+      <c r="P15" s="33" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>169</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E16" s="1">
         <v>1002001002</v>
@@ -5986,260 +6592,502 @@
         <v>3102001002</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>179</v>
+        <v>105</v>
+      </c>
+      <c r="V16" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="W16" s="30"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>170</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E17" s="1">
         <v>1002001003</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G17" s="1">
         <v>3102001004</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>180</v>
+        <v>106</v>
+      </c>
+      <c r="V17" s="43" t="s">
+        <v>329</v>
+      </c>
+      <c r="W17" s="31" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>171</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E18" s="1">
         <v>1002001005</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="G18" s="1">
         <v>3102001005</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
-        <v>181</v>
+        <v>107</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>172</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E19" s="1">
         <v>1002001007</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G19" s="1">
         <v>3102001008</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>182</v>
+        <v>108</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E20" s="1">
         <v>1002001009</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G20" s="1">
         <v>3102001009</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C22" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="29"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="15"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="W20" s="41" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V21" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="W21" s="41" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C22" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="V22" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="W22" s="41" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C23" s="11" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>93</v>
+        <v>174</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>391</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="W23" s="41" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C24" s="4" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>169</v>
+        <v>392</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>160</v>
       </c>
       <c r="G24" s="1">
         <v>3104567821</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="P24" s="15"/>
-      <c r="Q24" s="15"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H24" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="W24" s="41" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C25" s="4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D25" s="2">
         <v>2</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>118</v>
+        <v>393</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>111</v>
       </c>
       <c r="G25" s="1">
         <v>3115678932</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H25" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="W25" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C26" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D26" s="2">
         <v>2</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="F26" s="14" t="s">
-        <v>170</v>
+        <v>394</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>161</v>
       </c>
       <c r="G26" s="1">
         <v>3126789043</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="15"/>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H26" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C27" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D27" s="2">
         <v>2</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>121</v>
+        <v>395</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>114</v>
       </c>
       <c r="G27" s="1">
         <v>3137890154</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H27" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="V27" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="W27" s="30"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C28" s="4" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D28" s="2">
         <v>2</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>171</v>
+        <v>396</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>162</v>
       </c>
       <c r="G28" s="1">
         <v>3148901265</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>123</v>
+      <c r="H28" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="V28" s="31" t="s">
+        <v>361</v>
+      </c>
+      <c r="W28" s="31" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V29" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="W29" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V30" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="W30" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V31" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="W31" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V32" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="W32" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="33" spans="22:23" x14ac:dyDescent="0.25">
+      <c r="V33" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="W33" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="34" spans="22:23" x14ac:dyDescent="0.25">
+      <c r="V34" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="W34" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="35" spans="22:23" x14ac:dyDescent="0.25">
+      <c r="V35" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="W35" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="36" spans="22:23" x14ac:dyDescent="0.25">
+      <c r="V36" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="W36" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="37" spans="22:23" x14ac:dyDescent="0.25">
+      <c r="V37" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="W37" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="38" spans="22:23" x14ac:dyDescent="0.25">
+      <c r="V38" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="39" spans="22:23" x14ac:dyDescent="0.25">
+      <c r="V39" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="W39" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="40" spans="22:23" x14ac:dyDescent="0.25">
+      <c r="V40" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="W40" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="41" spans="22:23" x14ac:dyDescent="0.25">
+      <c r="V41" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="W41" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="42" spans="22:23" x14ac:dyDescent="0.25">
+      <c r="V42" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="W42" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="43" spans="22:23" x14ac:dyDescent="0.25">
+      <c r="V43" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="W43" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="44" spans="22:23" x14ac:dyDescent="0.25">
+      <c r="V44" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="W44" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="45" spans="22:23" x14ac:dyDescent="0.25">
+      <c r="V45" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="W45" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="46" spans="22:23" x14ac:dyDescent="0.25">
+      <c r="V46" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="W46" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="47" spans="22:23" x14ac:dyDescent="0.25">
+      <c r="V47" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="W47" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="48" spans="22:23" x14ac:dyDescent="0.25">
+      <c r="V48" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="W48" s="2" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="J1:R1"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="8">
+    <mergeCell ref="V1:W1"/>
     <mergeCell ref="A14:H14"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="K1:T1"/>
+    <mergeCell ref="C22:I22"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
@@ -6258,16 +7106,16 @@
     <hyperlink ref="F26" r:id="rId13" xr:uid="{0D677D5E-70C6-4F8F-96B9-7E5ADEE6D7D7}"/>
     <hyperlink ref="F27" r:id="rId14" display="mailto:contacto@refugioanimal.org" xr:uid="{08C51B59-44DA-43A1-95F9-4BA619EDF65E}"/>
     <hyperlink ref="F28" r:id="rId15" xr:uid="{DB2F7EDA-8C90-4BB2-8BD6-F9B735ADE1CC}"/>
-    <hyperlink ref="R3" r:id="rId16" display="mailto:carlos.mendez@correo.com" xr:uid="{55D341CE-B51A-4D52-8262-548599405DC6}"/>
-    <hyperlink ref="R4" r:id="rId17" display="mailto:andrea.castro@correo.com" xr:uid="{7A0F5B8C-02E2-4707-8D04-87B7F14CA29A}"/>
-    <hyperlink ref="R5" r:id="rId18" display="mailto:felipe.navarro@correo.com" xr:uid="{29CC5D05-321D-4A13-A99B-E37A08D52D50}"/>
-    <hyperlink ref="R6" r:id="rId19" display="mailto:laura.salazar@correo.com" xr:uid="{7280312C-B609-46F4-9EAD-D3566E139825}"/>
-    <hyperlink ref="R7" r:id="rId20" display="mailto:mauricio.torres@correo.com" xr:uid="{0556B5AC-89EC-42CF-B4DE-A52F558FF2D4}"/>
-    <hyperlink ref="R8" r:id="rId21" display="mailto:diana.rios@correo.com" xr:uid="{43EE3E3D-31CD-4B97-8715-034007A95CEF}"/>
-    <hyperlink ref="R9" r:id="rId22" display="mailto:jorge.vargas@correo.com" xr:uid="{2D13EE67-AF87-4E01-B1F3-97AEE87FE8E3}"/>
-    <hyperlink ref="R10" r:id="rId23" display="mailto:paula.herrera@correo.com" xr:uid="{A60960BD-C540-47A4-853A-816722DAF91D}"/>
-    <hyperlink ref="R11" r:id="rId24" display="mailto:sergio.leon@correo.com" xr:uid="{25686D0E-9C77-4497-AA0A-9AE8414D8C4D}"/>
-    <hyperlink ref="R12" r:id="rId25" display="mailto:marcela.duarte@correo.com" xr:uid="{FDAC968D-C4D6-48C0-BE34-569DD41ACD0D}"/>
+    <hyperlink ref="T3" r:id="rId16" display="mailto:carlos.mendez@correo.com" xr:uid="{55D341CE-B51A-4D52-8262-548599405DC6}"/>
+    <hyperlink ref="T4" r:id="rId17" display="mailto:andrea.castro@correo.com" xr:uid="{7A0F5B8C-02E2-4707-8D04-87B7F14CA29A}"/>
+    <hyperlink ref="T5" r:id="rId18" display="mailto:felipe.navarro@correo.com" xr:uid="{29CC5D05-321D-4A13-A99B-E37A08D52D50}"/>
+    <hyperlink ref="T6" r:id="rId19" display="mailto:laura.salazar@correo.com" xr:uid="{7280312C-B609-46F4-9EAD-D3566E139825}"/>
+    <hyperlink ref="T7" r:id="rId20" display="mailto:mauricio.torres@correo.com" xr:uid="{0556B5AC-89EC-42CF-B4DE-A52F558FF2D4}"/>
+    <hyperlink ref="T8" r:id="rId21" display="mailto:diana.rios@correo.com" xr:uid="{43EE3E3D-31CD-4B97-8715-034007A95CEF}"/>
+    <hyperlink ref="T9" r:id="rId22" display="mailto:jorge.vargas@correo.com" xr:uid="{2D13EE67-AF87-4E01-B1F3-97AEE87FE8E3}"/>
+    <hyperlink ref="T10" r:id="rId23" display="mailto:paula.herrera@correo.com" xr:uid="{A60960BD-C540-47A4-853A-816722DAF91D}"/>
+    <hyperlink ref="T11" r:id="rId24" display="mailto:sergio.leon@correo.com" xr:uid="{25686D0E-9C77-4497-AA0A-9AE8414D8C4D}"/>
+    <hyperlink ref="T12" r:id="rId25" display="mailto:marcela.duarte@correo.com" xr:uid="{FDAC968D-C4D6-48C0-BE34-569DD41ACD0D}"/>
     <hyperlink ref="F16" r:id="rId26" display="mailto:diego.perez@correo.com" xr:uid="{72055717-69DB-49DC-9CB6-C83722A88078}"/>
     <hyperlink ref="F17" r:id="rId27" display="mailto:julian.morales@correo.com" xr:uid="{00269101-2949-4FC1-B505-60754B3C598D}"/>
     <hyperlink ref="F18" r:id="rId28" display="mailto:sara.suarez@correo.com" xr:uid="{5894CFE5-A29B-4318-9072-DE3A55036948}"/>

--- a/2.DIAGRAMAS/PPP.xlsx
+++ b/2.DIAGRAMAS/PPP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aprendiz\Documents\ADSO, 2006\PROYECTO_ADSO_KJGA\2.DIAGRAMAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA2D77F-B0BC-41B5-814C-DBD22F3FAB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C198739-6CA1-42B7-ACEE-6691D6CFB744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D1012828-DDFC-47C0-86DB-3A2BD43233B1}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="440">
   <si>
     <t>Fundación</t>
   </si>
@@ -400,21 +400,9 @@
     <t>Fundacion</t>
   </si>
   <si>
-    <t>nom_Direc</t>
-  </si>
-  <si>
-    <t>apell_Direc</t>
-  </si>
-  <si>
     <t>id_Fund</t>
   </si>
   <si>
-    <t>doc_Direc</t>
-  </si>
-  <si>
-    <t>tel_Direc</t>
-  </si>
-  <si>
     <t>Sedes</t>
   </si>
   <si>
@@ -1295,6 +1283,84 @@
   </si>
   <si>
     <t>EP007</t>
+  </si>
+  <si>
+    <t>sexo</t>
+  </si>
+  <si>
+    <t>fechor_P</t>
+  </si>
+  <si>
+    <t>Mascota_Perdida</t>
+  </si>
+  <si>
+    <t>Hembra</t>
+  </si>
+  <si>
+    <t>Macho</t>
+  </si>
+  <si>
+    <t>nom_Dic</t>
+  </si>
+  <si>
+    <t>apell_Dic</t>
+  </si>
+  <si>
+    <t>doc_Dic</t>
+  </si>
+  <si>
+    <t>tel_Dic</t>
+  </si>
+  <si>
+    <t>Sexo</t>
+  </si>
+  <si>
+    <t>id_Sex</t>
+  </si>
+  <si>
+    <t>SX001</t>
+  </si>
+  <si>
+    <t>SX002</t>
+  </si>
+  <si>
+    <t>id_Mp</t>
+  </si>
+  <si>
+    <t>MP001</t>
+  </si>
+  <si>
+    <t>MP002</t>
+  </si>
+  <si>
+    <t>MP003</t>
+  </si>
+  <si>
+    <t>MP004</t>
+  </si>
+  <si>
+    <t>MP005</t>
+  </si>
+  <si>
+    <t>MP006</t>
+  </si>
+  <si>
+    <t>MP007</t>
+  </si>
+  <si>
+    <t>MP008</t>
+  </si>
+  <si>
+    <t>MP009</t>
+  </si>
+  <si>
+    <t>MP010</t>
+  </si>
+  <si>
+    <t>Maine_Coon</t>
+  </si>
+  <si>
+    <t>id_Clint</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +1533,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1482,30 +1548,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1556,6 +1598,15 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1620,9 +1671,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1640,49 +1688,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1691,17 +1706,45 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -2046,7 +2089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53CAFCBD-51ED-4D7F-B584-3F5A2EED76BE}">
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -2059,48 +2102,51 @@
     <col min="8" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
+    <col min="18" max="18" width="11.85546875" customWidth="1"/>
+    <col min="20" max="21" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-    </row>
-    <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+    </row>
+    <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E2" s="16" t="s">
         <v>0</v>
@@ -2108,52 +2154,55 @@
       <c r="F2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="I2" s="28" t="s">
+        <v>318</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>414</v>
+      </c>
+      <c r="L2" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="M2" s="27" t="s">
         <v>247</v>
       </c>
-      <c r="H2" s="39" t="s">
+      <c r="N2" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="I2" s="40" t="s">
-        <v>322</v>
-      </c>
-      <c r="J2" s="39" t="s">
+      <c r="O2" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="K2" s="39" t="s">
+      <c r="P2" s="28" t="s">
         <v>250</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="Q2" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="M2" s="39" t="s">
-        <v>252</v>
-      </c>
-      <c r="N2" s="39" t="s">
-        <v>253</v>
-      </c>
-      <c r="O2" s="40" t="s">
-        <v>254</v>
-      </c>
-      <c r="P2" s="40" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q2" s="40" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R2" s="28" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>6</v>
@@ -2162,51 +2211,55 @@
         <v>6</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I3" s="9" t="s">
         <v>39</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="O3" s="17">
+        <v>46270.604166666664</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="N3" s="8" t="s">
+      <c r="R3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T3" s="40"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>6</v>
@@ -2215,51 +2268,56 @@
         <v>6</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>333</v>
+      <c r="K4" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>264</v>
+        <v>329</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="N4" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="O4" s="17">
+        <v>46272.427083333336</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="O4" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T4" s="40"/>
+      <c r="U4" s="40"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>6</v>
@@ -2268,51 +2326,55 @@
         <v>6</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>334</v>
+        <v>262</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>267</v>
+        <v>330</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="N5" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="O5" s="17">
+        <v>46267.697916666664</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T5" s="40"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>6</v>
@@ -2321,51 +2383,55 @@
         <v>6</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>335</v>
+        <v>264</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>269</v>
+        <v>331</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="N6" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="O6" s="17">
+        <v>46266.805555555555</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="O6" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T6" s="40"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>6</v>
@@ -2374,40 +2440,45 @@
         <v>6</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>336</v>
+        <v>266</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="N7" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="O7" s="17">
+        <v>46271.479166666664</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="O7" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T7" s="40"/>
+      <c r="U7" s="40"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>3</v>
       </c>
@@ -2415,10 +2486,10 @@
         <v>11</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>6</v>
@@ -2427,51 +2498,55 @@
         <v>6</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>337</v>
+        <v>268</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>273</v>
+        <v>333</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="N8" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="O8" s="17">
+        <v>46269.361111111109</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="O8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T8" s="40"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>6</v>
@@ -2480,40 +2555,44 @@
         <v>6</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>338</v>
+        <v>270</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>275</v>
+        <v>334</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="N9" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="O9" s="17">
+        <v>46268.715277777781</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="O9" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q9" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T9" s="40"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>3</v>
       </c>
@@ -2521,10 +2600,10 @@
         <v>14</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>6</v>
@@ -2533,40 +2612,45 @@
         <v>6</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>339</v>
+        <v>272</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="N10" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="O10" s="17">
+        <v>46273.392361111109</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="O10" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T10" s="40"/>
+      <c r="U10" s="40"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>3</v>
       </c>
@@ -2574,10 +2658,10 @@
         <v>16</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>6</v>
@@ -2586,40 +2670,44 @@
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>340</v>
+        <v>274</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>279</v>
+        <v>336</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="N11" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="O11" s="17">
+        <v>46263.576388888891</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R11" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="O11" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T11" s="40"/>
+    </row>
+    <row r="12" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>3</v>
       </c>
@@ -2627,10 +2715,10 @@
         <v>18</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>6</v>
@@ -2639,146 +2727,159 @@
         <v>6</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>341</v>
+        <v>276</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>281</v>
+        <v>337</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="N12" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="O12" s="17">
+        <v>46265.753472222219</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R12" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="O12" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T12" s="40"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="J13" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="O13" s="17">
+        <v>46266.375</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q13" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R13" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="T13" s="40"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>343</v>
+        <v>256</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>286</v>
+        <v>339</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="N14" s="17">
+        <v>282</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="O14" s="17">
         <v>46280.375</v>
       </c>
-      <c r="O14" s="18">
+      <c r="P14" s="17">
         <v>46280.541666666664</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q14" s="9" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q14" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="T14" s="40"/>
+      <c r="U14" s="40"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>20</v>
       </c>
@@ -2786,52 +2887,57 @@
         <v>24</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>344</v>
+        <v>259</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>288</v>
+        <v>340</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q15" s="9" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+      <c r="O15" s="17">
+        <v>46244.4375</v>
+      </c>
+      <c r="P15" s="17">
+        <v>46270.680555555555</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R15" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>20</v>
       </c>
@@ -2839,158 +2945,172 @@
         <v>24</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>345</v>
+        <v>256</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>290</v>
+        <v>341</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="N16" s="17">
+        <v>286</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="O16" s="17">
         <v>46254.416666666664</v>
       </c>
-      <c r="O16" s="18">
+      <c r="P16" s="17">
         <v>46254.583333333336</v>
       </c>
-      <c r="P16" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q16" s="9" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q16" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R16" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="T16" s="40"/>
+      <c r="U16" s="40"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>29</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>346</v>
+        <v>262</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>260</v>
+        <v>280</v>
+      </c>
+      <c r="O17" s="17">
+        <v>46267.46875</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q17" s="9" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R17" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="T17" s="40"/>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>29</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>347</v>
+        <v>256</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>293</v>
+        <v>343</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="N18" s="17">
+        <v>289</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="O18" s="17">
         <v>46275.333333333336</v>
       </c>
-      <c r="O18" s="18">
+      <c r="P18" s="17">
         <v>46275.5</v>
       </c>
-      <c r="P18" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q18" s="9" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q18" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R18" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="T18" s="40"/>
+      <c r="U18" s="40"/>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>20</v>
       </c>
@@ -2998,52 +3118,56 @@
         <v>33</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>31</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>348</v>
+        <v>264</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>295</v>
+        <v>344</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>260</v>
+        <v>280</v>
+      </c>
+      <c r="O19" s="17">
+        <v>46268.597222222219</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q19" s="9" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R19" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="T19" s="40"/>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>20</v>
       </c>
@@ -3051,52 +3175,57 @@
         <v>33</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>31</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>349</v>
+        <v>256</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>296</v>
+        <v>345</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="N20" s="17">
+        <v>292</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="O20" s="17">
         <v>46283.458333333336</v>
       </c>
-      <c r="O20" s="18">
+      <c r="P20" s="17">
         <v>46283.625</v>
       </c>
-      <c r="P20" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q20" s="9" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q20" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R20" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="T20" s="40"/>
+      <c r="U20" s="40"/>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>20</v>
       </c>
@@ -3104,52 +3233,57 @@
         <v>36</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>38</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>350</v>
+        <v>266</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>297</v>
+        <v>346</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q21" s="9" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+      <c r="O21" s="17">
+        <v>46259.395833333336</v>
+      </c>
+      <c r="P21" s="17">
+        <v>46273.65625</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R21" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="T21" s="40"/>
+      <c r="U21" s="40"/>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>20</v>
       </c>
@@ -3157,105 +3291,114 @@
         <v>36</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>38</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>351</v>
+        <v>256</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>298</v>
+        <v>347</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="N22" s="18">
+        <v>294</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="O22" s="17">
         <v>46259.375</v>
       </c>
-      <c r="O22" s="18">
+      <c r="P22" s="17">
         <v>46259.541666666664</v>
       </c>
-      <c r="P22" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q22" s="9" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q22" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R22" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="T22" s="40"/>
+      <c r="U22" s="40"/>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="J23" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="O23" s="17">
+        <v>46266.375</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q23" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q23" s="9" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R23" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="T23" s="40"/>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>2</v>
       </c>
@@ -3263,52 +3406,57 @@
         <v>23</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>343</v>
+        <v>256</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>286</v>
+        <v>339</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="N24" s="17">
+        <v>282</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="O24" s="17">
         <v>46280.375</v>
       </c>
-      <c r="O24" s="18">
+      <c r="P24" s="17">
         <v>46280.541666666664</v>
       </c>
-      <c r="P24" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q24" s="9" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q24" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R24" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="T24" s="40"/>
+      <c r="U24" s="40"/>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>2</v>
       </c>
@@ -3316,52 +3464,57 @@
         <v>27</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>344</v>
+        <v>259</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>288</v>
+        <v>340</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q25" s="9" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+      <c r="O25" s="17">
+        <v>46244.4375</v>
+      </c>
+      <c r="P25" s="17">
+        <v>46270.680555555555</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R25" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="T25" s="40"/>
+      <c r="U25" s="40"/>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>2</v>
       </c>
@@ -3369,52 +3522,57 @@
         <v>28</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>26</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>345</v>
+        <v>256</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>290</v>
+        <v>341</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="N26" s="17">
+        <v>286</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="O26" s="17">
         <v>46254.416666666664</v>
       </c>
-      <c r="O26" s="18">
+      <c r="P26" s="17">
         <v>46254.583333333336</v>
       </c>
-      <c r="P26" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q26" s="9" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q26" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R26" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="T26" s="40"/>
+      <c r="U26" s="40"/>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>2</v>
       </c>
@@ -3422,105 +3580,114 @@
         <v>30</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>29</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>346</v>
+        <v>262</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>260</v>
+        <v>280</v>
+      </c>
+      <c r="O27" s="17">
+        <v>46267.46875</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q27" s="9" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R27" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="T27" s="40"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>29</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>347</v>
+        <v>256</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>293</v>
+        <v>343</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="N28" s="17">
+        <v>289</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="O28" s="17">
         <v>46275.333333333336</v>
       </c>
-      <c r="O28" s="18">
+      <c r="P28" s="17">
         <v>46275.5</v>
       </c>
-      <c r="P28" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q28" s="9" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q28" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R28" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="T28" s="40"/>
+      <c r="U28" s="40"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>2</v>
       </c>
@@ -3528,52 +3695,56 @@
         <v>32</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>31</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>348</v>
+        <v>264</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>295</v>
+        <v>344</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>260</v>
+        <v>280</v>
+      </c>
+      <c r="O29" s="17">
+        <v>46268.597222222219</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q29" s="9" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R29" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="T29" s="40"/>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>2</v>
       </c>
@@ -3581,105 +3752,115 @@
         <v>35</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>31</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>349</v>
+        <v>256</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>296</v>
+        <v>345</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="N30" s="17">
+        <v>292</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="O30" s="17">
         <v>46283.458333333336</v>
       </c>
-      <c r="O30" s="18">
+      <c r="P30" s="17">
         <v>46283.625</v>
       </c>
-      <c r="P30" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q30" s="9" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q30" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R30" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="T30" s="40"/>
+      <c r="U30" s="40"/>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>38</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>350</v>
+        <v>266</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>297</v>
+        <v>346</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q31" s="9" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+      <c r="O31" s="17">
+        <v>46259.395833333336</v>
+      </c>
+      <c r="P31" s="17">
+        <v>46273.65625</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R31" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="T31" s="40"/>
+      <c r="U31" s="40"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>2</v>
       </c>
@@ -3687,62 +3868,68 @@
         <v>40</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>38</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>351</v>
+        <v>256</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>298</v>
+        <v>347</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="N32" s="18">
+        <v>294</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="O32" s="17">
         <v>46259.375</v>
       </c>
-      <c r="O32" s="18">
+      <c r="P32" s="17">
         <v>46259.541666666664</v>
       </c>
-      <c r="P32" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q32" s="9" t="s">
-        <v>396</v>
-      </c>
+      <c r="Q32" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R32" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="T32" s="40"/>
+      <c r="U32" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CC2C4B9-5300-4C27-836E-2A9C35E8924B}">
-  <dimension ref="A1:T32"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -3758,102 +3945,106 @@
     <col min="11" max="11" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.42578125" style="3"/>
+    <col min="14" max="14" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-    </row>
-    <row r="2" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>326</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>324</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="D2" s="19" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+    </row>
+    <row r="2" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="E2" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="H2" s="21" t="s">
+      <c r="L2" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="M2" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="N2" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="P2" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q2" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="R2" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="S2" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="I2" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="K2" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="L2" s="22" t="s">
-        <v>307</v>
-      </c>
-      <c r="M2" s="21" t="s">
-        <v>299</v>
-      </c>
-      <c r="N2" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="O2" s="22" t="s">
+      <c r="T2" s="21" t="s">
         <v>302</v>
       </c>
-      <c r="P2" s="22" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q2" s="22" t="s">
-        <v>304</v>
-      </c>
-      <c r="R2" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="S2" s="22" t="s">
-        <v>306</v>
-      </c>
-      <c r="T2" s="22" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U2" s="21" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -3876,7 +4067,7 @@
         <v>3001001001</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>6</v>
@@ -3885,37 +4076,40 @@
         <v>6</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="L3" s="9" t="s">
         <v>39</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N3" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="O3" s="37" t="s">
+        <v>417</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="R3" s="41">
+        <v>46270.604166666664</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="T3" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="P3" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q3" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R3" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S3" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="T3" s="8" t="s">
+      <c r="U3" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
@@ -3938,7 +4132,7 @@
         <v>3001001002</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I4" s="8" t="s">
         <v>6</v>
@@ -3947,37 +4141,40 @@
         <v>6</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>265</v>
+        <v>259</v>
+      </c>
+      <c r="O4" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>260</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S4" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="T4" s="8" t="s">
+      <c r="R4" s="41">
+        <v>46272.427083333336</v>
+      </c>
+      <c r="S4" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T4" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="U4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
@@ -4000,7 +4197,7 @@
         <v>3001001003</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>6</v>
@@ -4009,37 +4206,40 @@
         <v>6</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>259</v>
+        <v>262</v>
+      </c>
+      <c r="O5" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>263</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R5" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S5" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="T5" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="R5" s="41">
+        <v>46267.697916666664</v>
+      </c>
+      <c r="S5" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T5" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
@@ -4062,7 +4262,7 @@
         <v>3001001004</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>6</v>
@@ -4071,37 +4271,40 @@
         <v>6</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="P6" s="9" t="s">
-        <v>259</v>
+        <v>264</v>
+      </c>
+      <c r="O6" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>265</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R6" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S6" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="T6" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="R6" s="41">
+        <v>46266.805555555555</v>
+      </c>
+      <c r="S6" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T6" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="U6" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>3</v>
       </c>
@@ -4124,7 +4327,7 @@
         <v>3001001005</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>6</v>
@@ -4133,37 +4336,40 @@
         <v>6</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
+      </c>
+      <c r="O7" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>267</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R7" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S7" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="T7" s="8" t="s">
+      <c r="R7" s="41">
+        <v>46271.479166666664</v>
+      </c>
+      <c r="S7" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T7" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>3</v>
       </c>
@@ -4186,7 +4392,7 @@
         <v>3001001006</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="I8" s="8" t="s">
         <v>6</v>
@@ -4195,37 +4401,40 @@
         <v>6</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>259</v>
+        <v>268</v>
+      </c>
+      <c r="O8" s="37" t="s">
+        <v>417</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>269</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R8" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S8" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="T8" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="R8" s="41">
+        <v>46269.361111111109</v>
+      </c>
+      <c r="S8" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T8" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="U8" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>3</v>
       </c>
@@ -4248,7 +4457,7 @@
         <v>3001001007</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>6</v>
@@ -4257,37 +4466,40 @@
         <v>6</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>259</v>
+        <v>270</v>
+      </c>
+      <c r="O9" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R9" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S9" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="T9" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="R9" s="41">
+        <v>46268.715277777781</v>
+      </c>
+      <c r="S9" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T9" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="U9" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>3</v>
       </c>
@@ -4310,7 +4522,7 @@
         <v>3001001008</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>6</v>
@@ -4319,37 +4531,40 @@
         <v>6</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>265</v>
+        <v>272</v>
+      </c>
+      <c r="O10" s="37" t="s">
+        <v>417</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R10" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S10" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="T10" s="8" t="s">
+      <c r="R10" s="41">
+        <v>46273.392361111109</v>
+      </c>
+      <c r="S10" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T10" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="U10" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>3</v>
       </c>
@@ -4372,7 +4587,7 @@
         <v>3001001009</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>6</v>
@@ -4381,37 +4596,40 @@
         <v>6</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="O11" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>259</v>
+        <v>274</v>
+      </c>
+      <c r="O11" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>275</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R11" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S11" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="T11" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="R11" s="41">
+        <v>46263.576388888891</v>
+      </c>
+      <c r="S11" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T11" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="U11" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>3</v>
       </c>
@@ -4434,7 +4652,7 @@
         <v>3001001010</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="I12" s="8" t="s">
         <v>6</v>
@@ -4443,37 +4661,40 @@
         <v>6</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="O12" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>259</v>
+        <v>438</v>
+      </c>
+      <c r="O12" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>277</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R12" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S12" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="T12" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="R12" s="41">
+        <v>46265.753472222219</v>
+      </c>
+      <c r="S12" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T12" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="U12" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>20</v>
       </c>
@@ -4489,53 +4710,56 @@
       <c r="E13" s="8">
         <v>1002001001</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="22" t="s">
         <v>21</v>
       </c>
       <c r="G13" s="8">
         <v>3102001001</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N13" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="O13" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="P13" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q13" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="R13" s="41">
+        <v>46266.375</v>
+      </c>
+      <c r="S13" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="T13" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="O13" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R13" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S13" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="T13" s="9" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U13" s="9" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>20</v>
       </c>
@@ -4551,53 +4775,56 @@
       <c r="E14" s="8">
         <v>1002001001</v>
       </c>
-      <c r="F14" s="23" t="s">
+      <c r="F14" s="22" t="s">
         <v>21</v>
       </c>
       <c r="G14" s="8">
         <v>3102001001</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="O14" s="23" t="s">
-        <v>286</v>
-      </c>
-      <c r="P14" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q14" s="24">
+        <v>256</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="P14" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="R14" s="41">
         <v>46280.375</v>
       </c>
-      <c r="R14" s="24">
+      <c r="S14" s="41">
         <v>46280.541666666664</v>
       </c>
-      <c r="S14" s="9" t="s">
-        <v>261</v>
-      </c>
       <c r="T14" s="9" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="U14" s="9" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>20</v>
       </c>
@@ -4613,53 +4840,56 @@
       <c r="E15" s="8">
         <v>1002001003</v>
       </c>
-      <c r="F15" s="23" t="s">
+      <c r="F15" s="22" t="s">
         <v>25</v>
       </c>
       <c r="G15" s="8">
         <v>3102001003</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="O15" s="23" t="s">
-        <v>288</v>
-      </c>
-      <c r="P15" s="9" t="s">
-        <v>289</v>
+        <v>259</v>
+      </c>
+      <c r="O15" s="37" t="s">
+        <v>417</v>
+      </c>
+      <c r="P15" s="22" t="s">
+        <v>284</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R15" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S15" s="9" t="s">
-        <v>261</v>
+        <v>285</v>
+      </c>
+      <c r="R15" s="41">
+        <v>46244.4375</v>
+      </c>
+      <c r="S15" s="41">
+        <v>46270.680555555555</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="U15" s="9" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>20</v>
       </c>
@@ -4675,53 +4905,56 @@
       <c r="E16" s="8">
         <v>1002001003</v>
       </c>
-      <c r="F16" s="23" t="s">
+      <c r="F16" s="22" t="s">
         <v>25</v>
       </c>
       <c r="G16" s="8">
         <v>3102001003</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="O16" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="P16" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q16" s="24">
+        <v>256</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="P16" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q16" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="R16" s="41">
         <v>46254.416666666664</v>
       </c>
-      <c r="R16" s="24">
+      <c r="S16" s="41">
         <v>46254.583333333336</v>
       </c>
-      <c r="S16" s="9" t="s">
-        <v>261</v>
-      </c>
       <c r="T16" s="9" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="U16" s="9" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>20</v>
       </c>
@@ -4737,53 +4970,56 @@
       <c r="E17" s="8">
         <v>1002001005</v>
       </c>
-      <c r="F17" s="23" t="s">
-        <v>175</v>
+      <c r="F17" s="22" t="s">
+        <v>171</v>
       </c>
       <c r="G17" s="8">
         <v>3102001005</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="O17" s="23" t="s">
-        <v>292</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>284</v>
+        <v>262</v>
+      </c>
+      <c r="O17" s="37" t="s">
+        <v>417</v>
+      </c>
+      <c r="P17" s="22" t="s">
+        <v>288</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R17" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S17" s="9" t="s">
-        <v>261</v>
+        <v>280</v>
+      </c>
+      <c r="R17" s="41">
+        <v>46267.46875</v>
+      </c>
+      <c r="S17" s="42" t="s">
+        <v>256</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="U17" s="9" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>20</v>
       </c>
@@ -4799,53 +5035,56 @@
       <c r="E18" s="8">
         <v>1002001005</v>
       </c>
-      <c r="F18" s="23" t="s">
-        <v>175</v>
+      <c r="F18" s="22" t="s">
+        <v>171</v>
       </c>
       <c r="G18" s="8">
         <v>3102001005</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="O18" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="P18" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q18" s="24">
+        <v>256</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="P18" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q18" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="R18" s="41">
         <v>46275.333333333336</v>
       </c>
-      <c r="R18" s="24">
+      <c r="S18" s="41">
         <v>46275.5</v>
       </c>
-      <c r="S18" s="9" t="s">
-        <v>261</v>
-      </c>
       <c r="T18" s="9" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="U18" s="9" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>20</v>
       </c>
@@ -4861,53 +5100,56 @@
       <c r="E19" s="8">
         <v>1002001007</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="F19" s="22" t="s">
         <v>34</v>
       </c>
       <c r="G19" s="8">
         <v>3102001007</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="O19" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="P19" s="9" t="s">
-        <v>284</v>
+        <v>264</v>
+      </c>
+      <c r="O19" s="37" t="s">
+        <v>417</v>
+      </c>
+      <c r="P19" s="22" t="s">
+        <v>291</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R19" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S19" s="9" t="s">
-        <v>261</v>
+        <v>280</v>
+      </c>
+      <c r="R19" s="41">
+        <v>46268.597222222219</v>
+      </c>
+      <c r="S19" s="42" t="s">
+        <v>256</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="U19" s="9" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>20</v>
       </c>
@@ -4923,53 +5165,56 @@
       <c r="E20" s="8">
         <v>1002001007</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="F20" s="22" t="s">
         <v>34</v>
       </c>
       <c r="G20" s="8">
         <v>3102001007</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="O20" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="P20" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q20" s="24">
+        <v>256</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="P20" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q20" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="R20" s="41">
         <v>46283.458333333336</v>
       </c>
-      <c r="R20" s="24">
+      <c r="S20" s="41">
         <v>46283.625</v>
       </c>
-      <c r="S20" s="9" t="s">
-        <v>261</v>
-      </c>
       <c r="T20" s="9" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="U20" s="9" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>20</v>
       </c>
@@ -4985,53 +5230,56 @@
       <c r="E21" s="8">
         <v>1002001009</v>
       </c>
-      <c r="F21" s="23" t="s">
+      <c r="F21" s="22" t="s">
         <v>37</v>
       </c>
       <c r="G21" s="8">
         <v>3102001009</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="O21" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>289</v>
+        <v>266</v>
+      </c>
+      <c r="O21" s="37" t="s">
+        <v>417</v>
+      </c>
+      <c r="P21" s="22" t="s">
+        <v>293</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R21" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S21" s="9" t="s">
-        <v>261</v>
+        <v>285</v>
+      </c>
+      <c r="R21" s="41">
+        <v>46259.395833333336</v>
+      </c>
+      <c r="S21" s="41">
+        <v>46273.65625</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="U21" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>20</v>
       </c>
@@ -5047,54 +5295,57 @@
       <c r="E22" s="8">
         <v>1002001009</v>
       </c>
-      <c r="F22" s="23" t="s">
+      <c r="F22" s="22" t="s">
         <v>37</v>
       </c>
       <c r="G22" s="8">
         <v>3102001009</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N22" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="O22" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="P22" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q22" s="24">
+        <v>256</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="P22" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="R22" s="41">
         <v>46259.375</v>
       </c>
-      <c r="R22" s="24">
+      <c r="S22" s="41">
         <v>46259.541666666664</v>
       </c>
-      <c r="S22" s="9" t="s">
-        <v>261</v>
-      </c>
       <c r="T22" s="9" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="U22" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" s="23" t="s">
         <v>2</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -5109,54 +5360,57 @@
       <c r="E23" s="8">
         <v>1003001001</v>
       </c>
-      <c r="F23" s="23" t="s">
-        <v>150</v>
+      <c r="F23" s="22" t="s">
+        <v>146</v>
       </c>
       <c r="G23" s="8">
         <v>3203001001</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N23" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="O23" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="P23" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q23" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="R23" s="41">
+        <v>46266.375</v>
+      </c>
+      <c r="S23" s="42" t="s">
+        <v>256</v>
+      </c>
+      <c r="T23" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="O23" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q23" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R23" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S23" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="T23" s="9" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
+      <c r="U23" s="9" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" s="23" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -5171,54 +5425,57 @@
       <c r="E24" s="8">
         <v>1003001002</v>
       </c>
-      <c r="F24" s="23" t="s">
-        <v>151</v>
+      <c r="F24" s="22" t="s">
+        <v>147</v>
       </c>
       <c r="G24" s="8">
         <v>3203001002</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="O24" s="23" t="s">
-        <v>286</v>
-      </c>
-      <c r="P24" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q24" s="24">
+        <v>256</v>
+      </c>
+      <c r="O24" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="P24" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q24" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="R24" s="41">
         <v>46280.375</v>
       </c>
-      <c r="R24" s="24">
+      <c r="S24" s="41">
         <v>46280.541666666664</v>
       </c>
-      <c r="S24" s="9" t="s">
-        <v>261</v>
-      </c>
       <c r="T24" s="9" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="U24" s="9" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="23" t="s">
         <v>2</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -5233,54 +5490,57 @@
       <c r="E25" s="8">
         <v>1003001003</v>
       </c>
-      <c r="F25" s="23" t="s">
-        <v>152</v>
+      <c r="F25" s="22" t="s">
+        <v>148</v>
       </c>
       <c r="G25" s="8">
         <v>3203001003</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="O25" s="23" t="s">
-        <v>288</v>
-      </c>
-      <c r="P25" s="9" t="s">
-        <v>289</v>
+        <v>259</v>
+      </c>
+      <c r="O25" s="37" t="s">
+        <v>417</v>
+      </c>
+      <c r="P25" s="22" t="s">
+        <v>284</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R25" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S25" s="9" t="s">
-        <v>261</v>
+        <v>285</v>
+      </c>
+      <c r="R25" s="41">
+        <v>46244.4375</v>
+      </c>
+      <c r="S25" s="41">
+        <v>46270.680555555555</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="U25" s="9" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" s="23" t="s">
         <v>2</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -5295,54 +5555,57 @@
       <c r="E26" s="8">
         <v>1003001004</v>
       </c>
-      <c r="F26" s="23" t="s">
-        <v>153</v>
+      <c r="F26" s="22" t="s">
+        <v>149</v>
       </c>
       <c r="G26" s="8">
         <v>3203001004</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="O26" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="P26" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q26" s="24">
+        <v>256</v>
+      </c>
+      <c r="O26" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="P26" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q26" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="R26" s="41">
         <v>46254.416666666664</v>
       </c>
-      <c r="R26" s="24">
+      <c r="S26" s="41">
         <v>46254.583333333336</v>
       </c>
-      <c r="S26" s="9" t="s">
-        <v>261</v>
-      </c>
       <c r="T26" s="9" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="U26" s="9" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" s="23" t="s">
         <v>2</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -5357,54 +5620,57 @@
       <c r="E27" s="8">
         <v>1003001005</v>
       </c>
-      <c r="F27" s="23" t="s">
-        <v>154</v>
+      <c r="F27" s="22" t="s">
+        <v>150</v>
       </c>
       <c r="G27" s="8">
         <v>3203001005</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="O27" s="23" t="s">
-        <v>292</v>
-      </c>
-      <c r="P27" s="9" t="s">
-        <v>284</v>
+        <v>262</v>
+      </c>
+      <c r="O27" s="37" t="s">
+        <v>417</v>
+      </c>
+      <c r="P27" s="22" t="s">
+        <v>288</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R27" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S27" s="9" t="s">
-        <v>261</v>
+        <v>280</v>
+      </c>
+      <c r="R27" s="41">
+        <v>46267.46875</v>
+      </c>
+      <c r="S27" s="42" t="s">
+        <v>256</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="U27" s="9" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="23" t="s">
         <v>2</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -5419,54 +5685,57 @@
       <c r="E28" s="8">
         <v>1003001006</v>
       </c>
-      <c r="F28" s="23" t="s">
-        <v>155</v>
+      <c r="F28" s="22" t="s">
+        <v>151</v>
       </c>
       <c r="G28" s="8">
         <v>3203001006</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N28" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="O28" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="P28" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q28" s="24">
+        <v>256</v>
+      </c>
+      <c r="O28" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="P28" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q28" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="R28" s="41">
         <v>46275.333333333336</v>
       </c>
-      <c r="R28" s="24">
+      <c r="S28" s="41">
         <v>46275.5</v>
       </c>
-      <c r="S28" s="9" t="s">
-        <v>261</v>
-      </c>
       <c r="T28" s="9" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A29" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="U28" s="9" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" s="23" t="s">
         <v>2</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -5481,54 +5750,57 @@
       <c r="E29" s="8">
         <v>1003001007</v>
       </c>
-      <c r="F29" s="23" t="s">
-        <v>156</v>
+      <c r="F29" s="22" t="s">
+        <v>152</v>
       </c>
       <c r="G29" s="8">
         <v>3203001007</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="O29" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="P29" s="9" t="s">
-        <v>284</v>
+        <v>264</v>
+      </c>
+      <c r="O29" s="37" t="s">
+        <v>417</v>
+      </c>
+      <c r="P29" s="22" t="s">
+        <v>291</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R29" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S29" s="9" t="s">
-        <v>261</v>
+        <v>280</v>
+      </c>
+      <c r="R29" s="41">
+        <v>46268.597222222219</v>
+      </c>
+      <c r="S29" s="42" t="s">
+        <v>256</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="U29" s="9" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" s="23" t="s">
         <v>2</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -5543,54 +5815,57 @@
       <c r="E30" s="8">
         <v>1003001008</v>
       </c>
-      <c r="F30" s="23" t="s">
-        <v>157</v>
+      <c r="F30" s="22" t="s">
+        <v>153</v>
       </c>
       <c r="G30" s="8">
         <v>3203001008</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N30" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="O30" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="P30" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q30" s="24">
+        <v>256</v>
+      </c>
+      <c r="O30" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="P30" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q30" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="R30" s="41">
         <v>46283.458333333336</v>
       </c>
-      <c r="R30" s="24">
+      <c r="S30" s="41">
         <v>46283.625</v>
       </c>
-      <c r="S30" s="9" t="s">
-        <v>261</v>
-      </c>
       <c r="T30" s="9" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="U30" s="9" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" s="23" t="s">
         <v>2</v>
       </c>
       <c r="B31" s="8" t="s">
@@ -5605,54 +5880,57 @@
       <c r="E31" s="8">
         <v>1003001009</v>
       </c>
-      <c r="F31" s="23" t="s">
-        <v>158</v>
+      <c r="F31" s="22" t="s">
+        <v>154</v>
       </c>
       <c r="G31" s="8">
         <v>3203001009</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="O31" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="P31" s="9" t="s">
-        <v>289</v>
+        <v>266</v>
+      </c>
+      <c r="O31" s="37" t="s">
+        <v>417</v>
+      </c>
+      <c r="P31" s="22" t="s">
+        <v>293</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="R31" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="S31" s="9" t="s">
-        <v>261</v>
+        <v>285</v>
+      </c>
+      <c r="R31" s="41">
+        <v>46259.395833333336</v>
+      </c>
+      <c r="S31" s="41">
+        <v>46273.65625</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="U31" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" s="23" t="s">
         <v>2</v>
       </c>
       <c r="B32" s="8" t="s">
@@ -5667,55 +5945,58 @@
       <c r="E32" s="8">
         <v>1003001010</v>
       </c>
-      <c r="F32" s="23" t="s">
-        <v>159</v>
+      <c r="F32" s="22" t="s">
+        <v>155</v>
       </c>
       <c r="G32" s="8">
         <v>3203001010</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N32" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="O32" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="P32" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q32" s="24">
+        <v>256</v>
+      </c>
+      <c r="O32" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="P32" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q32" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="R32" s="41">
         <v>46259.375</v>
       </c>
-      <c r="R32" s="24">
+      <c r="S32" s="41">
         <v>46259.541666666664</v>
       </c>
-      <c r="S32" s="9" t="s">
-        <v>261</v>
-      </c>
       <c r="T32" s="9" t="s">
-        <v>396</v>
+        <v>257</v>
+      </c>
+      <c r="U32" s="9" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A1:U1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F3" r:id="rId1" display="mailto:laura.gomez@correo.com" xr:uid="{4AF90779-ABB9-4953-AAF8-146090EC2F71}"/>
@@ -5752,7 +6033,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CCA6FB2-786D-496D-89D1-941A006DE469}">
-  <dimension ref="A1:W48"/>
+  <dimension ref="A1:X53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" style="15" customWidth="1"/>
@@ -5761,7 +6042,7 @@
     <col min="4" max="4" width="11.42578125" style="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.28515625" style="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="15" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="15" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.7109375" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.28515625" style="15" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.42578125" style="15" bestFit="1" customWidth="1"/>
@@ -5769,63 +6050,61 @@
     <col min="12" max="12" width="11" style="15" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.5703125" style="15" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="15" customWidth="1"/>
-    <col min="17" max="17" width="10.5703125" style="15" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="15" customWidth="1"/>
-    <col min="20" max="20" width="34.5703125" style="15" customWidth="1"/>
-    <col min="21" max="21" width="7.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" style="15" customWidth="1"/>
+    <col min="20" max="20" width="34.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.140625" style="15" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="9.7109375" style="15" customWidth="1"/>
-    <col min="23" max="23" width="20" style="15" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.7109375" style="15" customWidth="1"/>
-    <col min="25" max="25" width="20" style="15" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="20" style="15" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.7109375" style="15" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="20" style="15" bestFit="1" customWidth="1"/>
     <col min="28" max="16384" width="11.42578125" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1"/>
-      <c r="K1" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="35"/>
-      <c r="V1" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="W1" s="30"/>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1"/>
+      <c r="K1" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="33"/>
+      <c r="W1" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="X1" s="29"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>90</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>84</v>
@@ -5836,48 +6115,44 @@
       <c r="G2" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="I2"/>
       <c r="K2" s="11" t="s">
         <v>117</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="N2" s="11" t="s">
         <v>88</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>119</v>
+        <v>419</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>120</v>
+        <v>420</v>
       </c>
       <c r="Q2" s="11" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="R2" s="12" t="s">
-        <v>122</v>
+        <v>421</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>123</v>
+        <v>422</v>
       </c>
       <c r="T2" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="V2" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="W2" s="31" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W2" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="X2" s="24" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>91</v>
       </c>
@@ -5888,7 +6163,7 @@
         <v>41</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E3" s="1">
         <v>1001001001</v>
@@ -5899,21 +6174,17 @@
       <c r="G3" s="1">
         <v>3001001001</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="I3"/>
       <c r="K3" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>105</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>77</v>
@@ -5922,7 +6193,7 @@
         <v>72</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="R3" s="1">
         <v>1003001001</v>
@@ -5931,16 +6202,16 @@
         <v>3203001001</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="W3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="X3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>92</v>
       </c>
@@ -5951,7 +6222,7 @@
         <v>42</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E4" s="1">
         <v>1001001002</v>
@@ -5962,21 +6233,17 @@
       <c r="G4" s="1">
         <v>3001001002</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="I4"/>
       <c r="K4" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>105</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>78</v>
@@ -5985,7 +6252,7 @@
         <v>48</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="R4" s="1">
         <v>1003001002</v>
@@ -5994,16 +6261,16 @@
         <v>3203001002</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>93</v>
       </c>
@@ -6014,7 +6281,7 @@
         <v>43</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E5" s="1">
         <v>1001001003</v>
@@ -6025,21 +6292,17 @@
       <c r="G5" s="1">
         <v>3001001003</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="I5"/>
       <c r="K5" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>106</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>66</v>
@@ -6048,7 +6311,7 @@
         <v>53</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="R5" s="1">
         <v>1003001003</v>
@@ -6057,10 +6320,10 @@
         <v>3203001003</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>94</v>
       </c>
@@ -6071,32 +6334,28 @@
         <v>44</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E6" s="1">
         <v>1001001004</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G6" s="1">
         <v>3001001004</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="I6"/>
       <c r="K6" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>106</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>57</v>
@@ -6105,7 +6364,7 @@
         <v>55</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="R6" s="1">
         <v>1003001004</v>
@@ -6114,14 +6373,14 @@
         <v>3203001004</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="V6" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="W6" s="30"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="W6" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="X6" s="29"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>95</v>
       </c>
@@ -6132,7 +6391,7 @@
         <v>45</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E7" s="1">
         <v>1001001005</v>
@@ -6143,21 +6402,17 @@
       <c r="G7" s="1">
         <v>3001001005</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I7"/>
       <c r="K7" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>107</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>79</v>
@@ -6166,7 +6421,7 @@
         <v>46</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="R7" s="1">
         <v>1003001005</v>
@@ -6175,16 +6430,16 @@
         <v>3203001005</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="V7" s="31" t="s">
-        <v>409</v>
-      </c>
-      <c r="W7" s="31" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="W7" s="24" t="s">
+        <v>405</v>
+      </c>
+      <c r="X7" s="24" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>96</v>
       </c>
@@ -6195,7 +6450,7 @@
         <v>46</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E8" s="1">
         <v>1001001006</v>
@@ -6206,21 +6461,17 @@
       <c r="G8" s="1">
         <v>3001001006</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="I8"/>
       <c r="K8" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>107</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>80</v>
@@ -6229,7 +6480,7 @@
         <v>73</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="R8" s="1">
         <v>1003001006</v>
@@ -6238,16 +6489,16 @@
         <v>3203001006</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>411</v>
+        <v>151</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>97</v>
       </c>
@@ -6258,7 +6509,7 @@
         <v>47</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E9" s="1">
         <v>1001001007</v>
@@ -6269,21 +6520,17 @@
       <c r="G9" s="1">
         <v>3001001007</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="I9"/>
       <c r="K9" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>108</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>81</v>
@@ -6292,7 +6539,7 @@
         <v>50</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="R9" s="1">
         <v>1003001007</v>
@@ -6301,16 +6548,16 @@
         <v>3203001007</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>412</v>
+        <v>152</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+        <v>408</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>98</v>
       </c>
@@ -6321,7 +6568,7 @@
         <v>48</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E10" s="1">
         <v>1001001008</v>
@@ -6332,21 +6579,17 @@
       <c r="G10" s="1">
         <v>3001001008</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="I10"/>
       <c r="K10" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>108</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>65</v>
@@ -6355,7 +6598,7 @@
         <v>74</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="R10" s="1">
         <v>1003001008</v>
@@ -6364,16 +6607,16 @@
         <v>3203001008</v>
       </c>
       <c r="T10" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>413</v>
+        <v>153</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>99</v>
       </c>
@@ -6384,7 +6627,7 @@
         <v>49</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E11" s="1">
         <v>1001001009</v>
@@ -6395,21 +6638,17 @@
       <c r="G11" s="1">
         <v>3001001009</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="I11"/>
       <c r="K11" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>109</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>82</v>
@@ -6418,7 +6657,7 @@
         <v>75</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="R11" s="1">
         <v>1003001009</v>
@@ -6427,16 +6666,16 @@
         <v>3203001009</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>414</v>
+        <v>154</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+        <v>410</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>100</v>
       </c>
@@ -6447,7 +6686,7 @@
         <v>50</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E12" s="1">
         <v>1001001010</v>
@@ -6458,21 +6697,17 @@
       <c r="G12" s="1">
         <v>3001001010</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="I12"/>
       <c r="K12" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L12" s="4" t="s">
         <v>109</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>83</v>
@@ -6481,7 +6716,7 @@
         <v>76</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="R12" s="1">
         <v>1003001010</v>
@@ -6490,42 +6725,55 @@
         <v>3203001010</v>
       </c>
       <c r="T12" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>415</v>
+        <v>155</v>
       </c>
       <c r="W12" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="W13" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="K14" s="43" t="s">
+        <v>416</v>
+      </c>
+      <c r="L14" s="43"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="43"/>
+      <c r="Q14" s="43"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="43"/>
+      <c r="U14" s="43"/>
+      <c r="W14" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="X14" s="2" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="V13" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="W13" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="29"/>
-      <c r="V14" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="W14" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>101</v>
       </c>
@@ -6536,7 +6784,7 @@
         <v>103</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>104</v>
@@ -6548,30 +6796,45 @@
         <v>86</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="K15" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="L15" s="44" t="s">
-        <v>299</v>
-      </c>
-      <c r="M15" s="44" t="s">
-        <v>300</v>
-      </c>
-      <c r="N15" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="K15" s="26" t="s">
+        <v>427</v>
+      </c>
+      <c r="L15" s="26" t="s">
+        <v>439</v>
+      </c>
+      <c r="M15" s="25" t="s">
+        <v>357</v>
+      </c>
+      <c r="N15" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="O15" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="P15" s="26" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q15" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="R15" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="S15" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="T15" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="U15" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="O15" s="33" t="s">
-        <v>409</v>
-      </c>
-      <c r="P15" s="33" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>67</v>
@@ -6580,7 +6843,7 @@
         <v>51</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E16" s="1">
         <v>1002001002</v>
@@ -6594,14 +6857,47 @@
       <c r="H16" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="V16" s="42" t="s">
-        <v>248</v>
-      </c>
-      <c r="W16" s="30"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="K16" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="T16" s="17">
+        <v>46270.604166666664</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="W16" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="X16" s="29"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>68</v>
@@ -6610,7 +6906,7 @@
         <v>52</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E17" s="1">
         <v>1002001003</v>
@@ -6624,16 +6920,49 @@
       <c r="H17" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="V17" s="43" t="s">
-        <v>329</v>
-      </c>
-      <c r="W17" s="31" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K17" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="T17" s="17">
+        <v>46272.427083333336</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="W17" s="24" t="s">
+        <v>325</v>
+      </c>
+      <c r="X17" s="24" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>69</v>
@@ -6642,13 +6971,13 @@
         <v>54</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E18" s="1">
         <v>1002001005</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G18" s="1">
         <v>3102001005</v>
@@ -6656,16 +6985,49 @@
       <c r="H18" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="V18" s="2" t="s">
-        <v>330</v>
+      <c r="K18" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="T18" s="17">
+        <v>46267.697916666664</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>257</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+      <c r="X18" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>70</v>
@@ -6674,7 +7036,7 @@
         <v>55</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E19" s="1">
         <v>1002001007</v>
@@ -6688,16 +7050,49 @@
       <c r="H19" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="V19" s="2" t="s">
-        <v>331</v>
+      <c r="K19" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="T19" s="17">
+        <v>46266.805555555555</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>257</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+      <c r="X19" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>71</v>
@@ -6706,7 +7101,7 @@
         <v>56</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E20" s="1">
         <v>1002001009</v>
@@ -6720,47 +7115,146 @@
       <c r="H20" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="V20" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="W20" s="41" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="V21" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="W21" s="41" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C22" s="37" t="s">
+      <c r="K20" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="T20" s="17">
+        <v>46271.479166666664</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="X20" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="K21" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="T21" s="17">
+        <v>46269.361111111109</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C22" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="V22" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="W22" s="41" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="K22" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="T22" s="17">
+        <v>46268.715277777781</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C23" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="E23" s="36" t="s">
-        <v>391</v>
+        <v>170</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>387</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>85</v>
@@ -6772,16 +7266,49 @@
         <v>87</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="W23" s="41" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="T23" s="17">
+        <v>46273.392361111109</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="X23" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C24" s="4" t="s">
         <v>105</v>
       </c>
@@ -6789,28 +7316,61 @@
         <v>2</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G24" s="1">
         <v>3104567821</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V24" s="2" t="s">
+      <c r="K24" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="S24" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="W24" s="41" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T24" s="17">
+        <v>46263.576388888891</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C25" s="4" t="s">
         <v>106</v>
       </c>
@@ -6818,7 +7378,7 @@
         <v>2</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F25" s="13" t="s">
         <v>111</v>
@@ -6827,19 +7387,52 @@
         <v>3115678932</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="V25" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="W25" s="41" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="K25" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="T25" s="17">
+        <v>46265.753472222219</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="X25" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C26" s="4" t="s">
         <v>107</v>
       </c>
@@ -6847,22 +7440,22 @@
         <v>2</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G26" s="1">
         <v>3126789043</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C27" s="4" t="s">
         <v>108</v>
       </c>
@@ -6870,7 +7463,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>114</v>
@@ -6879,17 +7472,17 @@
         <v>3137890154</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="V27" s="30" t="s">
-        <v>250</v>
-      </c>
-      <c r="W27" s="30"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W27" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="X27" s="29"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C28" s="4" t="s">
         <v>109</v>
       </c>
@@ -6897,195 +7490,227 @@
         <v>2</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G28" s="1">
         <v>3148901265</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="V28" s="31" t="s">
+      <c r="W28" s="24" t="s">
+        <v>357</v>
+      </c>
+      <c r="X28" s="24" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="W29" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="X29" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="W30" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="X30" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="W31" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="X31" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="W32" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="X32" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="33" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W33" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="X33" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="34" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W34" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="X34" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="35" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W35" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="X35" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="W28" s="31" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="V29" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="W29" s="2" t="s">
+    </row>
+    <row r="36" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W36" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="X36" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="37" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W37" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="X37" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="38" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W38" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="X38" s="2" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="V30" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="W30" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="V31" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="W31" s="2" t="s">
+    <row r="39" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W39" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="X39" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="40" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W40" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="X40" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="41" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W41" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="X41" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="42" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W42" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="X42" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="43" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W43" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="X43" s="2" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="V32" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="W32" s="2" t="s">
+    <row r="44" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W44" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="X44" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="45" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W45" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="X45" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="46" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W46" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="X46" s="2" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="33" spans="22:23" x14ac:dyDescent="0.25">
-      <c r="V33" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="W33" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="34" spans="22:23" x14ac:dyDescent="0.25">
-      <c r="V34" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="W34" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="35" spans="22:23" x14ac:dyDescent="0.25">
-      <c r="V35" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="W35" s="2" t="s">
+    <row r="47" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W47" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="X47" s="2" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="36" spans="22:23" x14ac:dyDescent="0.25">
-      <c r="V36" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="W36" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="37" spans="22:23" x14ac:dyDescent="0.25">
-      <c r="V37" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="W37" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="38" spans="22:23" x14ac:dyDescent="0.25">
-      <c r="V38" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="W38" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="39" spans="22:23" x14ac:dyDescent="0.25">
-      <c r="V39" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="W39" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="40" spans="22:23" x14ac:dyDescent="0.25">
-      <c r="V40" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="W40" s="2" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="41" spans="22:23" x14ac:dyDescent="0.25">
-      <c r="V41" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="W41" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="42" spans="22:23" x14ac:dyDescent="0.25">
-      <c r="V42" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="W42" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="43" spans="22:23" x14ac:dyDescent="0.25">
-      <c r="V43" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="W43" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="44" spans="22:23" x14ac:dyDescent="0.25">
-      <c r="V44" s="2" t="s">
+    <row r="48" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W48" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="W44" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="45" spans="22:23" x14ac:dyDescent="0.25">
-      <c r="V45" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="W45" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="46" spans="22:23" x14ac:dyDescent="0.25">
-      <c r="V46" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="W46" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="47" spans="22:23" x14ac:dyDescent="0.25">
-      <c r="V47" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="W47" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="48" spans="22:23" x14ac:dyDescent="0.25">
-      <c r="V48" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="W48" s="2" t="s">
-        <v>336</v>
+      <c r="X48" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="50" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W50" s="29" t="s">
+        <v>423</v>
+      </c>
+      <c r="X50" s="29"/>
+    </row>
+    <row r="51" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W51" s="44" t="s">
+        <v>424</v>
+      </c>
+      <c r="X51" s="44" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="52" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W52" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="X52" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="53" spans="23:24" x14ac:dyDescent="0.25">
+      <c r="W53" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="X53" s="2" t="s">
+        <v>418</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="V1:W1"/>
+  <mergeCells count="10">
+    <mergeCell ref="W50:X50"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="K14:U14"/>
+    <mergeCell ref="W1:X1"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="W27:X27"/>
     <mergeCell ref="K1:T1"/>
     <mergeCell ref="C22:I22"/>
   </mergeCells>
